--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21DB167-CC59-465A-90B1-7FE417F101C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E26952-B5E6-46B8-853A-6C56E68CED7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -38,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Count</t>
   </si>
@@ -48,6 +70,21 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Words Remaining</t>
+  </si>
+  <si>
+    <t>Days Remaining (Deadline)</t>
+  </si>
+  <si>
+    <t>Days Remaining (Target)</t>
+  </si>
+  <si>
+    <t>Target Daily Rate</t>
+  </si>
+  <si>
+    <t>Deadline Daily Rate</t>
   </si>
 </sst>
 </file>
@@ -79,7 +116,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -95,6 +132,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -116,8 +159,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -178,14 +233,14 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -197,10 +252,38 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -240,19 +323,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -260,18 +368,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -280,8 +403,13 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFD18181"/>
+      <color rgb="FF76C886"/>
+      <color rgb="FF65E17A"/>
+      <color rgb="FF71F86A"/>
+      <color rgb="FFBEEEF8"/>
+      <color rgb="FF720808"/>
       <color rgb="FFF49E9E"/>
-      <color rgb="FFBEEEF8"/>
     </mruColors>
   </colors>
   <extLst>
@@ -326,13 +454,13 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-GB" b="1"/>
               <a:t>Word Count</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:overlay val="1"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -505,7 +633,7 @@
                   <c:v>1524</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2076</c:v>
+                  <c:v>2365</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -534,10 +662,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="tx2">
-                  <a:lumMod val="90000"/>
-                  <a:lumOff val="10000"/>
-                </a:schemeClr>
+                <a:srgbClr val="720808"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -700,7 +825,7 @@
         <c:axId val="1741707999"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="22000"/>
+          <c:max val="23000"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -1366,16 +1491,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>100011</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>183173</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>187933</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>161924</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>219808</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1720,261 +1845,323 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA3A3B3-C19C-41F0-9C7A-3F939AAD4664}">
-  <dimension ref="B1:D27"/>
+  <dimension ref="B1:G27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="21.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="2.85546875" style="26" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="24" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" style="25" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" style="26" customWidth="1"/>
+    <col min="5" max="5" width="2.85546875" style="26" customWidth="1"/>
+    <col min="6" max="6" width="27.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="8" t="s">
+    <row r="1" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+    </row>
+    <row r="2" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B3" s="4">
+      <c r="F2" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="27">
+        <f>COUNTIF(C3:C27, "")</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="7">
         <v>46250</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="21">
         <v>1524</v>
       </c>
-      <c r="D3" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="5">
+      <c r="D3" s="22">
+        <v>20000</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="28">
+        <f>COUNTIF(C3:C19, "")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="2">
         <v>46251</v>
       </c>
-      <c r="C4" s="7">
-        <v>2076</v>
-      </c>
-      <c r="D4" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" s="5">
+      <c r="C4" s="4">
+        <v>2365</v>
+      </c>
+      <c r="D4" s="9">
+        <v>20000</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="29" cm="1">
+        <f t="array" ref="G4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
+        <v>17635</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="B5" s="2">
         <v>46252</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" s="5">
+      <c r="C5" s="4"/>
+      <c r="D5" s="9">
+        <v>20000</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="20">
+        <f>ROUNDUP(G4/G3,0)</f>
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
         <v>46253</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B7" s="5">
+      <c r="C6" s="4"/>
+      <c r="D6" s="9">
+        <v>20000</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="19">
+        <f>ROUNDUP(G4/G2,0)</f>
+        <v>767</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="B7" s="8">
         <v>46254</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B8" s="5">
+      <c r="C7" s="23"/>
+      <c r="D7" s="22">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="2">
         <v>46255</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="10">
+      <c r="C8" s="4"/>
+      <c r="D8" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="2">
         <v>46256</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="10">
+      <c r="C9" s="4"/>
+      <c r="D9" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="B10" s="8">
         <v>46257</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B11" s="5">
+      <c r="C10" s="23"/>
+      <c r="D10" s="22">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B11" s="2">
         <v>46258</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B12" s="5">
+      <c r="C11" s="4"/>
+      <c r="D11" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="2">
         <v>46259</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B13" s="5">
+      <c r="C12" s="4"/>
+      <c r="D12" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="2">
         <v>46260</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="5">
+      <c r="C13" s="4"/>
+      <c r="D13" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="B14" s="8">
         <v>46261</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="5">
+      <c r="C14" s="23"/>
+      <c r="D14" s="22">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="2">
         <v>46262</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="10">
+      <c r="C15" s="4"/>
+      <c r="D15" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B16" s="2">
         <v>46263</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19">
+      <c r="C16" s="4"/>
+      <c r="D16" s="9">
         <v>20000</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="10">
+      <c r="B17" s="8">
         <v>46264</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="19">
+      <c r="C17" s="23"/>
+      <c r="D17" s="22">
         <v>20000</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="12">
+      <c r="B18" s="10">
         <v>46265</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="14">
+      <c r="C18" s="11"/>
+      <c r="D18" s="12">
         <v>20000</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="20">
+      <c r="B19" s="16">
         <v>46266</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22">
+      <c r="C19" s="17"/>
+      <c r="D19" s="18">
         <v>20000</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" s="4">
+      <c r="B20" s="1">
         <v>46267</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="5">
+      <c r="C20" s="3"/>
+      <c r="D20" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="B21" s="8">
         <v>46268</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="11">
+      <c r="C21" s="23"/>
+      <c r="D21" s="22">
         <v>20000</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B22" s="5">
+      <c r="B22" s="2">
         <v>46269</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="10">
+      <c r="C22" s="4"/>
+      <c r="D22" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="2">
         <v>46270</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="19">
+      <c r="C23" s="4"/>
+      <c r="D23" s="9">
         <v>20000</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="10">
+      <c r="B24" s="8">
         <v>46271</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="19">
+      <c r="C24" s="23"/>
+      <c r="D24" s="22">
         <v>20000</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="5">
+      <c r="B25" s="2">
         <v>46272</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="11">
+      <c r="C25" s="4"/>
+      <c r="D25" s="9">
         <v>20000</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="12">
+      <c r="B26" s="10">
         <v>46273</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="14">
+      <c r="C26" s="11"/>
+      <c r="D26" s="12">
         <v>20000</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="15">
+      <c r="B27" s="13">
         <v>46274</v>
       </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="17">
+      <c r="C27" s="14"/>
+      <c r="D27" s="15">
         <v>20000</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="250"/>
+        <cfvo type="num" val="500"/>
+        <color rgb="FF76C886"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFD18181"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="100"/>
+        <cfvo type="num" val="450"/>
+        <cfvo type="num" val="800"/>
+        <color rgb="FF76C886"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFD18181"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E26952-B5E6-46B8-853A-6C56E68CED7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A4759D-C6E7-4913-AF7E-3D2F365AE1F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Count</t>
   </si>
@@ -86,13 +86,16 @@
   <si>
     <t>Deadline Daily Rate</t>
   </si>
+  <si>
+    <t>Overall Target</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -172,7 +175,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -351,14 +354,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -367,16 +379,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -384,7 +396,7 @@
     <xf numFmtId="3" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -395,6 +407,7 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -635,6 +648,9 @@
                 <c:pt idx="1">
                   <c:v>2365</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>2663</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -650,11 +666,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$2</c:f>
+              <c:f>Sheet1!$E$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Target</c:v>
+                  <c:v>Overall Target</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -673,7 +689,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$3:$D$27</c:f>
+              <c:f>Sheet1!$E$3:$E$27</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="25"/>
@@ -1491,13 +1507,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>183173</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>187933</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>219808</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1845,300 +1861,347 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA3A3B3-C19C-41F0-9C7A-3F939AAD4664}">
-  <dimension ref="B1:G27"/>
+  <dimension ref="B1:H27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="26" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" style="24" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="26" customWidth="1"/>
-    <col min="5" max="5" width="2.85546875" style="26" customWidth="1"/>
-    <col min="6" max="6" width="27.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="26"/>
+    <col min="3" max="4" width="15.140625" style="25" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.85546875" style="26" customWidth="1"/>
+    <col min="7" max="7" width="27.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
-    </row>
-    <row r="2" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="26"/>
+    </row>
+    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="27">
+      <c r="H2" s="27">
         <f>COUNTIF(C3:C27, "")</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7">
         <v>46250</v>
       </c>
       <c r="C3" s="21">
         <v>1524</v>
       </c>
-      <c r="D3" s="22">
-        <v>20000</v>
-      </c>
-      <c r="F3" s="31" t="s">
+      <c r="D3" s="21"/>
+      <c r="E3" s="22">
+        <v>20000</v>
+      </c>
+      <c r="G3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="28">
+      <c r="H3" s="28">
         <f>COUNTIF(C3:C19, "")</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>46251</v>
       </c>
       <c r="C4" s="4">
         <v>2365</v>
       </c>
-      <c r="D4" s="9">
-        <v>20000</v>
-      </c>
-      <c r="F4" s="32" t="s">
+      <c r="D4" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E4" s="9">
+        <v>20000</v>
+      </c>
+      <c r="G4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="29" cm="1">
-        <f t="array" ref="G4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
-        <v>17635</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="H4" s="29" cm="1">
+        <f t="array" ref="H4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
+        <v>17337</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="15" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>46252</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="9">
-        <v>20000</v>
-      </c>
-      <c r="F5" s="33" t="s">
+      <c r="C5" s="3">
+        <v>2663</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E5" s="9">
+        <v>20000</v>
+      </c>
+      <c r="G5" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="20">
-        <f>ROUNDUP(G4/G3,0)</f>
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H5" s="20">
+        <f>ROUNDUP(H4/H3,0)</f>
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>46253</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="9">
-        <v>20000</v>
-      </c>
-      <c r="F6" s="34" t="s">
+      <c r="D6" s="3"/>
+      <c r="E6" s="9">
+        <v>20000</v>
+      </c>
+      <c r="G6" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="19">
-        <f>ROUNDUP(G4/G2,0)</f>
-        <v>767</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="H6" s="19">
+        <f>ROUNDUP(H4/H2,0)</f>
+        <v>789</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="15" x14ac:dyDescent="0.25">
       <c r="B7" s="8">
         <v>46254</v>
       </c>
       <c r="C7" s="23"/>
-      <c r="D7" s="22">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="D7" s="21"/>
+      <c r="E7" s="22">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>46255</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="9">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="3"/>
+      <c r="E8" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>46256</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="9">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="D9" s="3"/>
+      <c r="E9" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="15" x14ac:dyDescent="0.25">
       <c r="B10" s="8">
         <v>46257</v>
       </c>
       <c r="C10" s="23"/>
-      <c r="D10" s="22">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="D10" s="21"/>
+      <c r="E10" s="22">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B11" s="2">
         <v>46258</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="9">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="D11" s="3"/>
+      <c r="E11" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="2">
         <v>46259</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="9">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="D12" s="3"/>
+      <c r="E12" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>46260</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="9">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="D13" s="3"/>
+      <c r="E13" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="15" x14ac:dyDescent="0.25">
       <c r="B14" s="8">
         <v>46261</v>
       </c>
       <c r="C14" s="23"/>
-      <c r="D14" s="22">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="D14" s="21"/>
+      <c r="E14" s="22">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B15" s="2">
         <v>46262</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="9">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="D15" s="3"/>
+      <c r="E15" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B16" s="2">
         <v>46263</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="9">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="D16" s="3"/>
+      <c r="E16" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.25">
       <c r="B17" s="8">
         <v>46264</v>
       </c>
       <c r="C17" s="23"/>
-      <c r="D17" s="22">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D17" s="21"/>
+      <c r="E17" s="22">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10">
         <v>46265</v>
       </c>
       <c r="C18" s="11"/>
-      <c r="D18" s="12">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D18" s="35"/>
+      <c r="E18" s="12">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="16">
         <v>46266</v>
       </c>
       <c r="C19" s="17"/>
-      <c r="D19" s="18">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D19" s="17"/>
+      <c r="E19" s="18">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="1">
         <v>46267</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="9">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="D20" s="3"/>
+      <c r="E20" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.25">
       <c r="B21" s="8">
         <v>46268</v>
       </c>
       <c r="C21" s="23"/>
-      <c r="D21" s="22">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D21" s="21"/>
+      <c r="E21" s="22">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="2">
         <v>46269</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="9">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D22" s="3"/>
+      <c r="E22" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="2">
         <v>46270</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="9">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="D23" s="3"/>
+      <c r="E23" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.25">
       <c r="B24" s="8">
         <v>46271</v>
       </c>
       <c r="C24" s="23"/>
-      <c r="D24" s="22">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D24" s="21"/>
+      <c r="E24" s="22">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="2">
         <v>46272</v>
       </c>
       <c r="C25" s="4"/>
-      <c r="D25" s="9">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="3"/>
+      <c r="E25" s="9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="10">
         <v>46273</v>
       </c>
       <c r="C26" s="11"/>
-      <c r="D26" s="12">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D26" s="35"/>
+      <c r="E26" s="12">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B27" s="13">
         <v>46274</v>
       </c>
       <c r="C27" s="14"/>
-      <c r="D27" s="15">
+      <c r="D27" s="14"/>
+      <c r="E27" s="15">
         <v>20000</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G6">
+  <conditionalFormatting sqref="H5">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="100"/>
+        <cfvo type="num" val="450"/>
+        <cfvo type="num" val="800"/>
+        <color rgb="FF76C886"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFD18181"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2150,18 +2213,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="100"/>
-        <cfvo type="num" val="450"/>
-        <cfvo type="num" val="800"/>
-        <color rgb="FF76C886"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFD18181"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A4759D-C6E7-4913-AF7E-3D2F365AE1F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F189D661-95DE-4A7A-8D3D-6043AD12E266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>Count</t>
   </si>
@@ -88,6 +88,15 @@
   </si>
   <si>
     <t>Overall Target</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Daily Difference</t>
+  </si>
+  <si>
+    <t>Remaining Daily Count</t>
   </si>
 </sst>
 </file>
@@ -119,7 +128,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -174,6 +183,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF458ED7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="15">
     <border>
@@ -367,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -408,6 +423,10 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,13 +435,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF458ED7"/>
+      <color rgb="FF6BA5DF"/>
+      <color rgb="FFEE6868"/>
+      <color rgb="FFF18787"/>
+      <color rgb="FFF49E9E"/>
       <color rgb="FFD18181"/>
       <color rgb="FF76C886"/>
+      <color rgb="FF71F86A"/>
       <color rgb="FF65E17A"/>
-      <color rgb="FF71F86A"/>
       <color rgb="FFBEEEF8"/>
-      <color rgb="FF720808"/>
-      <color rgb="FFF49E9E"/>
     </mruColors>
   </colors>
   <extLst>
@@ -649,7 +671,10 @@
                   <c:v>2365</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2663</c:v>
+                  <c:v>2998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3250</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -666,7 +691,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$E$2</c:f>
+              <c:f>Sheet1!$G$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -689,7 +714,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$3:$E$27</c:f>
+              <c:f>Sheet1!$G$3:$G$27</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="25"/>
@@ -1507,13 +1532,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>183173</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>187933</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>219808</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1861,65 +1886,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA3A3B3-C19C-41F0-9C7A-3F939AAD4664}">
-  <dimension ref="B1:H27"/>
+  <dimension ref="B1:J27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="26" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" style="24" customWidth="1"/>
-    <col min="3" max="4" width="15.140625" style="25" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.85546875" style="26" customWidth="1"/>
-    <col min="7" max="7" width="27.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="26"/>
+    <col min="3" max="3" width="15.140625" style="25" customWidth="1"/>
+    <col min="4" max="4" width="16" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="25" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.85546875" style="26" customWidth="1"/>
+    <col min="9" max="9" width="27.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
-    </row>
-    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+    </row>
+    <row r="2" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="37" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="I2" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="27">
+      <c r="J2" s="27">
         <f>COUNTIF(C3:C27, "")</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7">
         <v>46250</v>
       </c>
       <c r="C3" s="21">
         <v>1524</v>
       </c>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22">
+      <c r="D3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="22">
         <v>20000</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="I3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="28">
+      <c r="J3" s="28">
         <f>COUNTIF(C3:C19, "")</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>46251</v>
       </c>
@@ -1927,270 +1971,466 @@
         <v>2365</v>
       </c>
       <c r="D4" s="3">
+        <f>IF(C4="", "", C4-C3)</f>
+        <v>841</v>
+      </c>
+      <c r="E4" s="3">
+        <f>IF(C4="", "", F4-C4)</f>
+        <v>-165</v>
+      </c>
+      <c r="F4" s="3">
         <v>2200</v>
       </c>
-      <c r="E4" s="9">
+      <c r="G4" s="9">
         <v>20000</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="I4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="29" cm="1">
-        <f t="array" ref="H4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
-        <v>17337</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="J4" s="29" cm="1">
+        <f t="array" ref="J4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
+        <v>16750</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>46252</v>
       </c>
       <c r="C5" s="3">
-        <v>2663</v>
+        <v>2998</v>
       </c>
       <c r="D5" s="3">
+        <f t="shared" ref="D5:D27" si="0">IF(C5="", "", C5-C4)</f>
+        <v>633</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" ref="E5:E27" si="1">IF(C5="", "", F5-C5)</f>
+        <v>202</v>
+      </c>
+      <c r="F5" s="3">
         <v>3200</v>
       </c>
-      <c r="E5" s="9">
+      <c r="G5" s="9">
         <v>20000</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="I5" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="20">
-        <f>ROUNDUP(H4/H3,0)</f>
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J5" s="20">
+        <f>ROUNDUP(J4/J3,0)</f>
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>46253</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="9">
+      <c r="C6" s="4">
+        <v>3250</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" si="0"/>
+        <v>252</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
+      <c r="F6" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G6" s="9">
         <v>20000</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="I6" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="19">
-        <f>ROUNDUP(H4/H2,0)</f>
-        <v>789</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="J6" s="19">
+        <f>ROUNDUP(J4/J2,0)</f>
+        <v>798</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B7" s="8">
         <v>46254</v>
       </c>
       <c r="C7" s="23"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="22">
+      <c r="D7" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E7" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F7" s="21"/>
+      <c r="G7" s="22">
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>46255</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="9">
+      <c r="D8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E8" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>46256</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="9">
+      <c r="D9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E9" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B10" s="8">
         <v>46257</v>
       </c>
       <c r="C10" s="23"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="22">
+      <c r="D10" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E10" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F10" s="21"/>
+      <c r="G10" s="22">
         <v>20000</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="2">
         <v>46258</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="9">
+      <c r="D11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E11" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="2">
         <v>46259</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="9">
+      <c r="D12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E12" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>46260</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="9">
+      <c r="D13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E13" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B14" s="8">
         <v>46261</v>
       </c>
       <c r="C14" s="23"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="22">
+      <c r="D14" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E14" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F14" s="21"/>
+      <c r="G14" s="22">
         <v>20000</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="2">
         <v>46262</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="9">
+      <c r="D15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E15" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2">
         <v>46263</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="9">
+      <c r="D16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E16" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" ht="15" x14ac:dyDescent="0.25">
       <c r="B17" s="8">
         <v>46264</v>
       </c>
       <c r="C17" s="23"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="22">
+      <c r="D17" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E17" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F17" s="21"/>
+      <c r="G17" s="22">
         <v>20000</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10">
         <v>46265</v>
       </c>
       <c r="C18" s="11"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="12">
+      <c r="D18" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E18" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F18" s="35"/>
+      <c r="G18" s="12">
         <v>20000</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="16">
         <v>46266</v>
       </c>
       <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18">
+      <c r="D19" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E19" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F19" s="17"/>
+      <c r="G19" s="18">
         <v>20000</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="1">
         <v>46267</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="9">
+      <c r="D20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E20" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" ht="15" x14ac:dyDescent="0.25">
       <c r="B21" s="8">
         <v>46268</v>
       </c>
       <c r="C21" s="23"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="22">
+      <c r="D21" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E21" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F21" s="21"/>
+      <c r="G21" s="22">
         <v>20000</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B22" s="2">
         <v>46269</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="9">
+      <c r="D22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E22" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="2">
         <v>46270</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="9">
+      <c r="D23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E23" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" ht="15" x14ac:dyDescent="0.25">
       <c r="B24" s="8">
         <v>46271</v>
       </c>
       <c r="C24" s="23"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="22">
+      <c r="D24" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E24" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="G24" s="22">
         <v>20000</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25" s="2">
         <v>46272</v>
       </c>
       <c r="C25" s="4"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="9">
+      <c r="D25" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="26" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="10">
         <v>46273</v>
       </c>
       <c r="C26" s="11"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="12">
+      <c r="D26" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E26" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F26" s="35"/>
+      <c r="G26" s="12">
         <v>20000</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B27" s="13">
         <v>46274</v>
       </c>
       <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="15">
+      <c r="D27" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E27" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="15">
         <v>20000</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="J5">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="100"/>
         <cfvo type="num" val="450"/>
@@ -2201,8 +2441,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="J6">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="250"/>
@@ -2213,6 +2453,30 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D27">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="500"/>
+        <cfvo type="num" val="900"/>
+        <cfvo type="num" val="1300"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E27">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="100"/>
+        <cfvo type="num" val="200"/>
+        <color rgb="FF76C886"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFEE6868"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F189D661-95DE-4A7A-8D3D-6043AD12E266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A05853-96E8-43C5-ACCC-6B53417AD9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
+    <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -93,10 +93,10 @@
     <t>NA</t>
   </si>
   <si>
-    <t>Daily Difference</t>
+    <t>Daily Count</t>
   </si>
   <si>
-    <t>Remaining Daily Count</t>
+    <t>Remaining Daily Target</t>
   </si>
 </sst>
 </file>
@@ -674,7 +674,10 @@
                   <c:v>2998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3250</c:v>
+                  <c:v>3611</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3611</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1892,8 +1895,8 @@
     <col min="1" max="1" width="2.85546875" style="26" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" style="24" customWidth="1"/>
     <col min="3" max="3" width="15.140625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="16" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" style="25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.140625" style="25" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" style="26" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="2.85546875" style="26" customWidth="1"/>
@@ -1933,7 +1936,7 @@
       </c>
       <c r="J2" s="27">
         <f>COUNTIF(C3:C27, "")</f>
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1960,7 +1963,7 @@
       </c>
       <c r="J3" s="28">
         <f>COUNTIF(C3:C19, "")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -1989,7 +1992,7 @@
       </c>
       <c r="J4" s="29" cm="1">
         <f t="array" ref="J4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
-        <v>16750</v>
+        <v>16389</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="15" x14ac:dyDescent="0.25">
@@ -2018,7 +2021,7 @@
       </c>
       <c r="J5" s="20">
         <f>ROUNDUP(J4/J3,0)</f>
-        <v>1289</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2026,15 +2029,15 @@
         <v>46253</v>
       </c>
       <c r="C6" s="4">
-        <v>3250</v>
+        <v>3611</v>
       </c>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
-        <v>252</v>
+        <v>613</v>
       </c>
       <c r="E6" s="3">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>389</v>
       </c>
       <c r="F6" s="3">
         <v>4000</v>
@@ -2047,23 +2050,27 @@
       </c>
       <c r="J6" s="19">
         <f>ROUNDUP(J4/J2,0)</f>
-        <v>798</v>
+        <v>820</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B7" s="8">
         <v>46254</v>
       </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="36" t="str">
+      <c r="C7" s="23">
+        <v>3611</v>
+      </c>
+      <c r="D7" s="36">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="36" t="str">
+        <v>0</v>
+      </c>
+      <c r="E7" s="36">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21"/>
+        <v>1389</v>
+      </c>
+      <c r="F7" s="21">
+        <v>5000</v>
+      </c>
       <c r="G7" s="22">
         <v>20000</v>
       </c>
@@ -2429,6 +2436,30 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D4:D27">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="500"/>
+        <cfvo type="num" val="900"/>
+        <cfvo type="num" val="1300"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E27">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="100"/>
+        <cfvo type="num" val="200"/>
+        <color rgb="FF76C886"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFEE6868"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J5">
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -2453,30 +2484,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D27">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="num" val="500"/>
-        <cfvo type="num" val="900"/>
-        <cfvo type="num" val="1300"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E27">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="100"/>
-        <cfvo type="num" val="200"/>
-        <color rgb="FF76C886"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFEE6868"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A05853-96E8-43C5-ACCC-6B53417AD9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379AB5D1-C99F-4A1E-BAA0-FF8A4A21E38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Count</t>
   </si>
@@ -96,7 +96,10 @@
     <t>Daily Count</t>
   </si>
   <si>
-    <t>Remaining Daily Target</t>
+    <t>Remaining Daily Count</t>
+  </si>
+  <si>
+    <t>Prop. Written</t>
   </si>
 </sst>
 </file>
@@ -382,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -423,10 +426,15 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -677,7 +685,7 @@
                   <c:v>3611</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3611</c:v>
+                  <c:v>4051</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -694,7 +702,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$2</c:f>
+              <c:f>Sheet1!$H$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -717,7 +725,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$3:$G$27</c:f>
+              <c:f>Sheet1!$H$3:$H$27</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="25"/>
@@ -1535,13 +1543,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>183173</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>187933</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>219808</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1889,34 +1897,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA3A3B3-C19C-41F0-9C7A-3F939AAD4664}">
-  <dimension ref="B1:J27"/>
+  <dimension ref="B1:K27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="26" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" style="24" customWidth="1"/>
     <col min="3" max="3" width="15.140625" style="25" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" style="25" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="25" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.85546875" style="26" customWidth="1"/>
-    <col min="9" max="9" width="27.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="26"/>
+    <col min="5" max="5" width="22.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="25" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" style="25" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.85546875" style="26" customWidth="1"/>
+    <col min="10" max="10" width="27.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
       <c r="E1" s="26"/>
       <c r="F1" s="26"/>
-    </row>
-    <row r="2" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G1" s="26"/>
+    </row>
+    <row r="2" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="36" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="6" t="s">
@@ -1925,21 +1935,24 @@
       <c r="E2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="J2" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="27">
+      <c r="K2" s="27">
         <f>COUNTIF(C3:C27, "")</f>
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7">
         <v>46250</v>
       </c>
@@ -1955,18 +1968,21 @@
       <c r="F3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="22">
         <v>20000</v>
       </c>
-      <c r="I3" s="31" t="s">
+      <c r="J3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="28">
+      <c r="K3" s="28">
         <f>COUNTIF(C3:C19, "")</f>
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>46251</v>
       </c>
@@ -1978,24 +1994,28 @@
         <v>841</v>
       </c>
       <c r="E4" s="3">
-        <f>IF(C4="", "", F4-C4)</f>
+        <f>IF(C4="", "", G4-C4)</f>
         <v>-165</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="38">
+        <f>D4 / (G4-C3)</f>
+        <v>1.2440828402366864</v>
+      </c>
+      <c r="G4" s="3">
         <v>2200</v>
       </c>
-      <c r="G4" s="9">
+      <c r="H4" s="9">
         <v>20000</v>
       </c>
-      <c r="I4" s="32" t="s">
+      <c r="J4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="29" cm="1">
-        <f t="array" ref="J4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
-        <v>16389</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="K4" s="29" cm="1">
+        <f t="array" ref="K4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
+        <v>15949</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>46252</v>
       </c>
@@ -2007,24 +2027,28 @@
         <v>633</v>
       </c>
       <c r="E5" s="3">
-        <f t="shared" ref="E5:E27" si="1">IF(C5="", "", F5-C5)</f>
+        <f t="shared" ref="E5:E27" si="1">IF(C5="", "", G5-C5)</f>
         <v>202</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="38">
+        <f t="shared" ref="F5:F7" si="2">D5 / (G5-C4)</f>
+        <v>0.75808383233532939</v>
+      </c>
+      <c r="G5" s="3">
         <v>3200</v>
       </c>
-      <c r="G5" s="9">
+      <c r="H5" s="9">
         <v>20000</v>
       </c>
-      <c r="I5" s="33" t="s">
+      <c r="J5" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="20">
-        <f>ROUNDUP(J4/J3,0)</f>
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K5" s="20">
+        <f>ROUNDUP(K4/K3,0)</f>
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>46253</v>
       </c>
@@ -2039,43 +2063,51 @@
         <f t="shared" si="1"/>
         <v>389</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="38">
+        <f t="shared" si="2"/>
+        <v>0.61177644710578838</v>
+      </c>
+      <c r="G6" s="3">
         <v>4000</v>
       </c>
-      <c r="G6" s="9">
+      <c r="H6" s="9">
         <v>20000</v>
       </c>
-      <c r="I6" s="34" t="s">
+      <c r="J6" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="19">
-        <f>ROUNDUP(J4/J2,0)</f>
-        <v>820</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="K6" s="19">
+        <f>ROUNDUP(K4/K2,0)</f>
+        <v>798</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B7" s="8">
         <v>46254</v>
       </c>
       <c r="C7" s="23">
-        <v>3611</v>
-      </c>
-      <c r="D7" s="36">
+        <v>4051</v>
+      </c>
+      <c r="D7" s="37">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E7" s="36">
+        <v>440</v>
+      </c>
+      <c r="E7" s="37">
         <f t="shared" si="1"/>
-        <v>1389</v>
-      </c>
-      <c r="F7" s="21">
+        <v>949</v>
+      </c>
+      <c r="F7" s="38">
+        <f t="shared" si="2"/>
+        <v>0.31677465802735782</v>
+      </c>
+      <c r="G7" s="21">
         <v>5000</v>
       </c>
-      <c r="G7" s="22">
+      <c r="H7" s="22">
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>46255</v>
       </c>
@@ -2088,12 +2120,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="9">
+      <c r="F8" s="38"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>46256</v>
       </c>
@@ -2106,30 +2139,32 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="9">
+      <c r="F9" s="38"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B10" s="8">
         <v>46257</v>
       </c>
       <c r="C10" s="23"/>
-      <c r="D10" s="36" t="str">
+      <c r="D10" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E10" s="36" t="str">
+      <c r="E10" s="37" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="22">
+      <c r="F10" s="39"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22">
         <v>20000</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="2">
         <v>46258</v>
       </c>
@@ -2142,12 +2177,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="9">
+      <c r="F11" s="38"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="2">
         <v>46259</v>
       </c>
@@ -2160,12 +2196,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="9">
+      <c r="F12" s="38"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>46260</v>
       </c>
@@ -2178,30 +2215,32 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="9">
+      <c r="F13" s="38"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="14" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B14" s="8">
         <v>46261</v>
       </c>
       <c r="C14" s="23"/>
-      <c r="D14" s="36" t="str">
+      <c r="D14" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E14" s="36" t="str">
+      <c r="E14" s="37" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="22">
+      <c r="F14" s="39"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22">
         <v>20000</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="2">
         <v>46262</v>
       </c>
@@ -2214,12 +2253,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="9">
+      <c r="F15" s="38"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="2">
         <v>46263</v>
       </c>
@@ -2232,30 +2272,32 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="9">
+      <c r="F16" s="38"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" ht="15" x14ac:dyDescent="0.25">
       <c r="B17" s="8">
         <v>46264</v>
       </c>
       <c r="C17" s="23"/>
-      <c r="D17" s="36" t="str">
+      <c r="D17" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E17" s="36" t="str">
+      <c r="E17" s="37" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F17" s="21"/>
-      <c r="G17" s="22">
+      <c r="F17" s="39"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22">
         <v>20000</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10">
         <v>46265</v>
       </c>
@@ -2268,12 +2310,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F18" s="35"/>
-      <c r="G18" s="12">
+      <c r="F18" s="40"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="12">
         <v>20000</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="16">
         <v>46266</v>
       </c>
@@ -2286,12 +2329,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18">
+      <c r="F19" s="41"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18">
         <v>20000</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="1">
         <v>46267</v>
       </c>
@@ -2304,30 +2348,32 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="9">
+      <c r="F20" s="38"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" ht="15" x14ac:dyDescent="0.25">
       <c r="B21" s="8">
         <v>46268</v>
       </c>
       <c r="C21" s="23"/>
-      <c r="D21" s="36" t="str">
+      <c r="D21" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E21" s="36" t="str">
+      <c r="E21" s="37" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F21" s="21"/>
-      <c r="G21" s="22">
+      <c r="F21" s="39"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="22">
         <v>20000</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="2">
         <v>46269</v>
       </c>
@@ -2340,12 +2386,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="9">
+      <c r="F22" s="38"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="2">
         <v>46270</v>
       </c>
@@ -2358,30 +2405,32 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="9">
+      <c r="F23" s="38"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" ht="15" x14ac:dyDescent="0.25">
       <c r="B24" s="8">
         <v>46271</v>
       </c>
       <c r="C24" s="23"/>
-      <c r="D24" s="36" t="str">
+      <c r="D24" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E24" s="36" t="str">
+      <c r="E24" s="37" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="22">
+      <c r="F24" s="39"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="22">
         <v>20000</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="2">
         <v>46272</v>
       </c>
@@ -2394,12 +2443,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="9">
+      <c r="F25" s="38"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="9">
         <v>20000</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="10">
         <v>46273</v>
       </c>
@@ -2412,12 +2462,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F26" s="35"/>
-      <c r="G26" s="12">
+      <c r="F26" s="40"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="12">
         <v>20000</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B27" s="13">
         <v>46274</v>
       </c>
@@ -2430,14 +2481,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15">
+      <c r="F27" s="42"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="15">
         <v>20000</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D4:D27">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="500"/>
         <cfvo type="num" val="900"/>
@@ -2449,7 +2501,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E27">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="100"/>
@@ -2460,8 +2512,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="K5">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="100"/>
         <cfvo type="num" val="450"/>
@@ -2472,8 +2524,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="K6">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="250"/>
@@ -2484,6 +2536,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F4:F27">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.75"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379AB5D1-C99F-4A1E-BAA0-FF8A4A21E38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B88B8DD-2E6B-42CA-9C76-FE169B54E758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -66,9 +66,6 @@
     <t>Count</t>
   </si>
   <si>
-    <t>Target</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -99,7 +96,10 @@
     <t>Remaining Daily Count</t>
   </si>
   <si>
-    <t>Prop. Written</t>
+    <t>PCT Written</t>
+  </si>
+  <si>
+    <t>Daily Target</t>
   </si>
 </sst>
 </file>
@@ -131,7 +131,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,25 +170,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF458ED7"/>
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1DECD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,56 +391,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -443,16 +446,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFF49E9E"/>
+      <color rgb="FFE1DECD"/>
+      <color rgb="FFFFFF99"/>
+      <color rgb="FF63BE7B"/>
+      <color rgb="FFFFEB84"/>
+      <color rgb="FFF8696B"/>
       <color rgb="FF458ED7"/>
       <color rgb="FF6BA5DF"/>
       <color rgb="FFEE6868"/>
       <color rgb="FFF18787"/>
-      <color rgb="FFF49E9E"/>
-      <color rgb="FFD18181"/>
-      <color rgb="FF76C886"/>
-      <color rgb="FF71F86A"/>
-      <color rgb="FF65E17A"/>
-      <color rgb="FFBEEEF8"/>
     </mruColors>
   </colors>
   <extLst>
@@ -685,7 +688,7 @@
                   <c:v>3611</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4051</c:v>
+                  <c:v>5050</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1900,84 +1903,84 @@
   <dimension ref="B1:K27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" style="24" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="25" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="25" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" style="25" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.85546875" style="26" customWidth="1"/>
-    <col min="10" max="10" width="27.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="26"/>
+    <col min="1" max="1" width="2.85546875" style="25" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="23" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="24" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="24" customWidth="1"/>
+    <col min="5" max="5" width="27" style="24" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="24" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="24" customWidth="1"/>
+    <col min="8" max="8" width="16" style="25" customWidth="1"/>
+    <col min="9" max="9" width="2.85546875" style="25" customWidth="1"/>
+    <col min="10" max="10" width="27.140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="2" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="36" t="s">
+      <c r="B2" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" s="27">
+      <c r="H2" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="11">
         <f>COUNTIF(C3:C27, "")</f>
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7">
+      <c r="B3" s="3">
         <v>46250</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="26">
         <v>1524</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="22">
+      <c r="D3" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="21">
         <v>20000</v>
       </c>
-      <c r="J3" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="28">
+      <c r="J3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="12">
         <f>COUNTIF(C3:C19, "")</f>
         <v>12</v>
       </c>
@@ -1986,143 +1989,146 @@
       <c r="B4" s="2">
         <v>46251</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="35">
         <v>2365</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="27">
         <f>IF(C4="", "", C4-C3)</f>
         <v>841</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="27">
         <f>IF(C4="", "", G4-C4)</f>
         <v>-165</v>
       </c>
-      <c r="F4" s="38">
-        <f>D4 / (G4-C3)</f>
+      <c r="F4" s="28">
+        <f t="shared" ref="F4:F8" si="0">IF(G4="","",IF(C4="","",D4/(G4-C3)))</f>
         <v>1.2440828402366864</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="36">
         <v>2200</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="20">
         <v>20000</v>
       </c>
-      <c r="J4" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" s="29" cm="1">
+      <c r="J4" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" s="13" cm="1">
         <f t="array" ref="K4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
-        <v>15949</v>
+        <v>14950</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>46252</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="36">
         <v>2998</v>
       </c>
-      <c r="D5" s="3">
-        <f t="shared" ref="D5:D27" si="0">IF(C5="", "", C5-C4)</f>
+      <c r="D5" s="27">
+        <f t="shared" ref="D5:D27" si="1">IF(C5="", "", C5-C4)</f>
         <v>633</v>
       </c>
-      <c r="E5" s="3">
-        <f t="shared" ref="E5:E27" si="1">IF(C5="", "", G5-C5)</f>
+      <c r="E5" s="27">
+        <f t="shared" ref="E5:E27" si="2">IF(C5="", "", G5-C5)</f>
         <v>202</v>
       </c>
-      <c r="F5" s="38">
-        <f t="shared" ref="F5:F7" si="2">D5 / (G5-C4)</f>
+      <c r="F5" s="28">
+        <f t="shared" si="0"/>
         <v>0.75808383233532939</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="36">
         <v>3200</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="20">
         <v>20000</v>
       </c>
-      <c r="J5" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="20">
+      <c r="J5" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="10">
         <f>ROUNDUP(K4/K3,0)</f>
-        <v>1330</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>46253</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="35">
         <v>3611</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="27">
+        <f t="shared" si="1"/>
+        <v>613</v>
+      </c>
+      <c r="E6" s="27">
+        <f t="shared" si="2"/>
+        <v>389</v>
+      </c>
+      <c r="F6" s="28">
         <f t="shared" si="0"/>
-        <v>613</v>
-      </c>
-      <c r="E6" s="3">
-        <f t="shared" si="1"/>
-        <v>389</v>
-      </c>
-      <c r="F6" s="38">
-        <f t="shared" si="2"/>
         <v>0.61177644710578838</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="36">
         <v>4000</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="20">
         <v>20000</v>
       </c>
-      <c r="J6" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="19">
+      <c r="J6" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="9">
         <f>ROUNDUP(K4/K2,0)</f>
-        <v>798</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="B7" s="8">
+      <c r="B7" s="4">
         <v>46254</v>
       </c>
-      <c r="C7" s="23">
-        <v>4051</v>
-      </c>
-      <c r="D7" s="37">
+      <c r="C7" s="39">
+        <v>5050</v>
+      </c>
+      <c r="D7" s="29">
+        <f t="shared" si="1"/>
+        <v>1439</v>
+      </c>
+      <c r="E7" s="29">
+        <f t="shared" si="2"/>
+        <v>-50</v>
+      </c>
+      <c r="F7" s="34">
         <f t="shared" si="0"/>
-        <v>440</v>
-      </c>
-      <c r="E7" s="37">
-        <f t="shared" si="1"/>
-        <v>949</v>
-      </c>
-      <c r="F7" s="38">
-        <f t="shared" si="2"/>
-        <v>0.31677465802735782</v>
-      </c>
-      <c r="G7" s="21">
+        <v>1.0359971202303815</v>
+      </c>
+      <c r="G7" s="40">
         <v>5000</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>46255</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="3" t="str">
+      <c r="C8" s="35"/>
+      <c r="D8" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="E8" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F8" s="28" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E8" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="38"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="9">
+      <c r="G8" s="36"/>
+      <c r="H8" s="20">
         <v>20000</v>
       </c>
     </row>
@@ -2130,37 +2136,43 @@
       <c r="B9" s="2">
         <v>46256</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="3" t="str">
+      <c r="C9" s="35"/>
+      <c r="D9" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F9" s="38"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="9">
+      <c r="E9" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F9" s="28" t="str">
+        <f t="shared" ref="F9:F27" si="3">IF(G9="","",IF(C9="","",D9/(G9-C8)))</f>
+        <v/>
+      </c>
+      <c r="G9" s="36"/>
+      <c r="H9" s="20">
         <v>20000</v>
       </c>
     </row>
     <row r="10" spans="2:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="8">
+      <c r="B10" s="4">
         <v>46257</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="37" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="37" t="str">
+      <c r="C10" s="39"/>
+      <c r="D10" s="29" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F10" s="39"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="22">
+      <c r="E10" s="29" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F10" s="34" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G10" s="40"/>
+      <c r="H10" s="21">
         <v>20000</v>
       </c>
     </row>
@@ -2168,18 +2180,21 @@
       <c r="B11" s="2">
         <v>46258</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="3" t="str">
+      <c r="C11" s="35"/>
+      <c r="D11" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F11" s="38"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="9">
+      <c r="E11" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F11" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G11" s="36"/>
+      <c r="H11" s="20">
         <v>20000</v>
       </c>
     </row>
@@ -2187,18 +2202,21 @@
       <c r="B12" s="2">
         <v>46259</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="3" t="str">
+      <c r="C12" s="35"/>
+      <c r="D12" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F12" s="38"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="9">
+      <c r="E12" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F12" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G12" s="36"/>
+      <c r="H12" s="20">
         <v>20000</v>
       </c>
     </row>
@@ -2206,37 +2224,43 @@
       <c r="B13" s="2">
         <v>46260</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="3" t="str">
+      <c r="C13" s="35"/>
+      <c r="D13" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F13" s="38"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="9">
+      <c r="E13" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F13" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G13" s="36"/>
+      <c r="H13" s="20">
         <v>20000</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="B14" s="8">
+      <c r="B14" s="4">
         <v>46261</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="37" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="37" t="str">
+      <c r="C14" s="39"/>
+      <c r="D14" s="29" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F14" s="39"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="22">
+      <c r="E14" s="29" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F14" s="34" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G14" s="40"/>
+      <c r="H14" s="21">
         <v>20000</v>
       </c>
     </row>
@@ -2244,18 +2268,21 @@
       <c r="B15" s="2">
         <v>46262</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="3" t="str">
+      <c r="C15" s="35"/>
+      <c r="D15" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F15" s="38"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="9">
+      <c r="E15" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F15" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G15" s="36"/>
+      <c r="H15" s="20">
         <v>20000</v>
       </c>
     </row>
@@ -2263,75 +2290,87 @@
       <c r="B16" s="2">
         <v>46263</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="3" t="str">
+      <c r="C16" s="35"/>
+      <c r="D16" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F16" s="38"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="9">
+      <c r="E16" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F16" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G16" s="36"/>
+      <c r="H16" s="20">
         <v>20000</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="8">
+      <c r="B17" s="4">
         <v>46264</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="37" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="37" t="str">
+      <c r="C17" s="39"/>
+      <c r="D17" s="29" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="22">
+      <c r="E17" s="29" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F17" s="34" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G17" s="40"/>
+      <c r="H17" s="21">
         <v>20000</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="10">
+      <c r="B18" s="5">
         <v>46265</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="35" t="str">
+      <c r="C18" s="37"/>
+      <c r="D18" s="30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="12">
+      <c r="E18" s="30" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F18" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G18" s="38"/>
+      <c r="H18" s="22">
         <v>20000</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="16">
+      <c r="B19" s="6">
         <v>46266</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E19" s="18" t="str">
+      <c r="C19" s="7"/>
+      <c r="D19" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F19" s="41"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="18">
+      <c r="E19" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F19" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="41">
         <v>20000</v>
       </c>
     </row>
@@ -2339,37 +2378,43 @@
       <c r="B20" s="1">
         <v>46267</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E20" s="3" t="str">
+      <c r="C20" s="36"/>
+      <c r="D20" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F20" s="38"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="9">
+      <c r="E20" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F20" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G20" s="36"/>
+      <c r="H20" s="20">
         <v>20000</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="8">
+      <c r="B21" s="4">
         <v>46268</v>
       </c>
-      <c r="C21" s="23"/>
-      <c r="D21" s="37" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E21" s="37" t="str">
+      <c r="C21" s="39"/>
+      <c r="D21" s="29" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F21" s="39"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="22">
+      <c r="E21" s="29" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F21" s="34" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G21" s="40"/>
+      <c r="H21" s="21">
         <v>20000</v>
       </c>
     </row>
@@ -2377,18 +2422,21 @@
       <c r="B22" s="2">
         <v>46269</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E22" s="3" t="str">
+      <c r="C22" s="35"/>
+      <c r="D22" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F22" s="38"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="9">
+      <c r="E22" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F22" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G22" s="36"/>
+      <c r="H22" s="20">
         <v>20000</v>
       </c>
     </row>
@@ -2396,37 +2444,43 @@
       <c r="B23" s="2">
         <v>46270</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E23" s="3" t="str">
+      <c r="C23" s="35"/>
+      <c r="D23" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F23" s="38"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="9">
+      <c r="E23" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F23" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G23" s="36"/>
+      <c r="H23" s="20">
         <v>20000</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="8">
+      <c r="B24" s="4">
         <v>46271</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="37" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E24" s="37" t="str">
+      <c r="C24" s="39"/>
+      <c r="D24" s="29" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="22">
+      <c r="E24" s="29" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F24" s="34" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G24" s="40"/>
+      <c r="H24" s="21">
         <v>20000</v>
       </c>
     </row>
@@ -2434,56 +2488,65 @@
       <c r="B25" s="2">
         <v>46272</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E25" s="3" t="str">
+      <c r="C25" s="35"/>
+      <c r="D25" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F25" s="38"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="9">
+      <c r="E25" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F25" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G25" s="36"/>
+      <c r="H25" s="20">
         <v>20000</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="10">
+      <c r="B26" s="5">
         <v>46273</v>
       </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E26" s="35" t="str">
+      <c r="C26" s="37"/>
+      <c r="D26" s="30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="12">
+      <c r="E26" s="30" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F26" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="22">
         <v>20000</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="13">
+      <c r="B27" s="6">
         <v>46274</v>
       </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E27" s="15" t="str">
+      <c r="C27" s="7"/>
+      <c r="D27" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F27" s="42"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="15">
+      <c r="E27" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F27" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="41">
         <v>20000</v>
       </c>
     </row>
@@ -2506,9 +2569,9 @@
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="100"/>
         <cfvo type="num" val="200"/>
-        <color rgb="FF76C886"/>
+        <color rgb="FF63BE7B"/>
         <color rgb="FFFFEB84"/>
-        <color rgb="FFEE6868"/>
+        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -2518,9 +2581,9 @@
         <cfvo type="num" val="100"/>
         <cfvo type="num" val="450"/>
         <cfvo type="num" val="800"/>
-        <color rgb="FF76C886"/>
+        <color rgb="FF63BE7B"/>
         <color rgb="FFFFEB84"/>
-        <color rgb="FFD18181"/>
+        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -2530,9 +2593,9 @@
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="250"/>
         <cfvo type="num" val="500"/>
-        <color rgb="FF76C886"/>
+        <color rgb="FF63BE7B"/>
         <color rgb="FFFFEB84"/>
-        <color rgb="FFD18181"/>
+        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B88B8DD-2E6B-42CA-9C76-FE169B54E758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719647DD-2FB2-4A66-B5F7-EB2947207B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -391,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -399,7 +399,6 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -431,13 +430,31 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -689,6 +706,12 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5050</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5610</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5786</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1903,232 +1926,236 @@
   <dimension ref="B1:K27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="25" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" style="23" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="24" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="24" customWidth="1"/>
-    <col min="5" max="5" width="27" style="24" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="24" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="24" customWidth="1"/>
-    <col min="8" max="8" width="16" style="25" customWidth="1"/>
-    <col min="9" max="9" width="2.85546875" style="25" customWidth="1"/>
-    <col min="10" max="10" width="27.140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="1" width="2.85546875" style="24" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="22" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="23" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="23" customWidth="1"/>
+    <col min="5" max="5" width="27" style="23" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="23" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="23" customWidth="1"/>
+    <col min="8" max="8" width="16" style="24" customWidth="1"/>
+    <col min="9" max="9" width="2.85546875" style="24" customWidth="1"/>
+    <col min="10" max="10" width="27.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="24"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="10">
         <f>COUNTIF(C3:C27, "")</f>
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
         <v>46250</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="39">
         <v>1524</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="21">
+      <c r="H3" s="20">
         <v>20000</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="11">
         <f>COUNTIF(C3:C19, "")</f>
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>46251</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="40">
         <v>2365</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="26">
         <f>IF(C4="", "", C4-C3)</f>
         <v>841</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="26">
         <f>IF(C4="", "", G4-C4)</f>
         <v>-165</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="27">
         <f t="shared" ref="F4:F8" si="0">IF(G4="","",IF(C4="","",D4/(G4-C3)))</f>
         <v>1.2440828402366864</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="35">
         <v>2200</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="19">
         <v>20000</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="13" cm="1">
+      <c r="K4" s="12" cm="1">
         <f t="array" ref="K4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
-        <v>14950</v>
+        <v>14214</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>46252</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="35">
         <v>2998</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="26">
         <f t="shared" ref="D5:D27" si="1">IF(C5="", "", C5-C4)</f>
         <v>633</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="26">
         <f t="shared" ref="E5:E27" si="2">IF(C5="", "", G5-C5)</f>
         <v>202</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="27">
         <f t="shared" si="0"/>
         <v>0.75808383233532939</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="35">
         <v>3200</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="19">
         <v>20000</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="9">
         <f>ROUNDUP(K4/K3,0)</f>
-        <v>1246</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>46253</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="40">
         <v>3611</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="26">
         <f t="shared" si="1"/>
         <v>613</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="26">
         <f t="shared" si="2"/>
         <v>389</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="27">
         <f t="shared" si="0"/>
         <v>0.61177644710578838</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="35">
         <v>4000</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="19">
         <v>20000</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="8">
         <f>ROUNDUP(K4/K2,0)</f>
-        <v>748</v>
+        <v>790</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>46254</v>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="41">
         <v>5050</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="28">
         <f t="shared" si="1"/>
         <v>1439</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="28">
         <f t="shared" si="2"/>
         <v>-50</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="33">
         <f t="shared" si="0"/>
         <v>1.0359971202303815</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="36">
         <v>5000</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="20">
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>46255</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="29" t="str">
+      <c r="C8" s="40">
+        <v>5610</v>
+      </c>
+      <c r="D8" s="26">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E8" s="27" t="str">
+        <v>560</v>
+      </c>
+      <c r="E8" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F8" s="28" t="str">
+        <v>790</v>
+      </c>
+      <c r="F8" s="27">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="36"/>
-      <c r="H8" s="20">
+        <v>0.4148148148148148</v>
+      </c>
+      <c r="G8" s="35">
+        <v>6400</v>
+      </c>
+      <c r="H8" s="19">
         <v>20000</v>
       </c>
     </row>
@@ -2136,21 +2163,25 @@
       <c r="B9" s="2">
         <v>46256</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="27" t="str">
+      <c r="C9" s="40">
+        <v>5786</v>
+      </c>
+      <c r="D9" s="26">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E9" s="27" t="str">
+        <v>176</v>
+      </c>
+      <c r="E9" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F9" s="28" t="str">
+        <v>1214</v>
+      </c>
+      <c r="F9" s="27">
         <f t="shared" ref="F9:F27" si="3">IF(G9="","",IF(C9="","",D9/(G9-C8)))</f>
-        <v/>
-      </c>
-      <c r="G9" s="36"/>
-      <c r="H9" s="20">
+        <v>0.12661870503597122</v>
+      </c>
+      <c r="G9" s="35">
+        <v>7000</v>
+      </c>
+      <c r="H9" s="19">
         <v>20000</v>
       </c>
     </row>
@@ -2158,21 +2189,21 @@
       <c r="B10" s="4">
         <v>46257</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="29" t="str">
+      <c r="C10" s="41"/>
+      <c r="D10" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E10" s="29" t="str">
+      <c r="E10" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F10" s="34" t="str">
+      <c r="F10" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G10" s="40"/>
-      <c r="H10" s="21">
+      <c r="G10" s="36"/>
+      <c r="H10" s="20">
         <v>20000</v>
       </c>
     </row>
@@ -2180,21 +2211,21 @@
       <c r="B11" s="2">
         <v>46258</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="27" t="str">
+      <c r="C11" s="40"/>
+      <c r="D11" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E11" s="27" t="str">
+      <c r="E11" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F11" s="28" t="str">
+      <c r="F11" s="27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G11" s="36"/>
-      <c r="H11" s="20">
+      <c r="G11" s="35"/>
+      <c r="H11" s="19">
         <v>20000</v>
       </c>
     </row>
@@ -2202,21 +2233,21 @@
       <c r="B12" s="2">
         <v>46259</v>
       </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="27" t="str">
+      <c r="C12" s="40"/>
+      <c r="D12" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E12" s="27" t="str">
+      <c r="E12" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F12" s="28" t="str">
+      <c r="F12" s="27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G12" s="36"/>
-      <c r="H12" s="20">
+      <c r="G12" s="35"/>
+      <c r="H12" s="19">
         <v>20000</v>
       </c>
     </row>
@@ -2224,21 +2255,21 @@
       <c r="B13" s="2">
         <v>46260</v>
       </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="27" t="str">
+      <c r="C13" s="40"/>
+      <c r="D13" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E13" s="27" t="str">
+      <c r="E13" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F13" s="28" t="str">
+      <c r="F13" s="27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G13" s="36"/>
-      <c r="H13" s="20">
+      <c r="G13" s="35"/>
+      <c r="H13" s="19">
         <v>20000</v>
       </c>
     </row>
@@ -2246,21 +2277,21 @@
       <c r="B14" s="4">
         <v>46261</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="29" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E14" s="29" t="str">
+      <c r="C14" s="41"/>
+      <c r="D14" s="28" t="str">
+        <f>IF(C14="", "", C14-C13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F14" s="34" t="str">
+      <c r="F14" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G14" s="40"/>
-      <c r="H14" s="21">
+      <c r="G14" s="36"/>
+      <c r="H14" s="20">
         <v>20000</v>
       </c>
     </row>
@@ -2268,21 +2299,21 @@
       <c r="B15" s="2">
         <v>46262</v>
       </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="27" t="str">
+      <c r="C15" s="40"/>
+      <c r="D15" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E15" s="27" t="str">
+      <c r="E15" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F15" s="28" t="str">
+      <c r="F15" s="27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G15" s="36"/>
-      <c r="H15" s="20">
+      <c r="G15" s="35"/>
+      <c r="H15" s="19">
         <v>20000</v>
       </c>
     </row>
@@ -2290,21 +2321,21 @@
       <c r="B16" s="2">
         <v>46263</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="27" t="str">
+      <c r="C16" s="40"/>
+      <c r="D16" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E16" s="27" t="str">
+      <c r="E16" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F16" s="28" t="str">
+      <c r="F16" s="27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G16" s="36"/>
-      <c r="H16" s="20">
+      <c r="G16" s="35"/>
+      <c r="H16" s="19">
         <v>20000</v>
       </c>
     </row>
@@ -2312,21 +2343,21 @@
       <c r="B17" s="4">
         <v>46264</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="29" t="str">
+      <c r="C17" s="41"/>
+      <c r="D17" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E17" s="29" t="str">
+      <c r="E17" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F17" s="34" t="str">
+      <c r="F17" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G17" s="40"/>
-      <c r="H17" s="21">
+      <c r="G17" s="36"/>
+      <c r="H17" s="20">
         <v>20000</v>
       </c>
     </row>
@@ -2334,21 +2365,21 @@
       <c r="B18" s="5">
         <v>46265</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="30" t="str">
+      <c r="C18" s="42"/>
+      <c r="D18" s="29" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E18" s="30" t="str">
+      <c r="E18" s="29" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F18" s="31" t="str">
+      <c r="F18" s="30" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="22">
+      <c r="G18" s="37"/>
+      <c r="H18" s="21">
         <v>20000</v>
       </c>
     </row>
@@ -2356,21 +2387,21 @@
       <c r="B19" s="6">
         <v>46266</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8" t="str">
+      <c r="C19" s="38"/>
+      <c r="D19" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E19" s="8" t="str">
+      <c r="E19" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F19" s="19" t="str">
+      <c r="F19" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="41">
+      <c r="G19" s="38"/>
+      <c r="H19" s="34">
         <v>20000</v>
       </c>
     </row>
@@ -2378,21 +2409,21 @@
       <c r="B20" s="1">
         <v>46267</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="27" t="str">
+      <c r="C20" s="35"/>
+      <c r="D20" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E20" s="27" t="str">
+      <c r="E20" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F20" s="28" t="str">
+      <c r="F20" s="27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G20" s="36"/>
-      <c r="H20" s="20">
+      <c r="G20" s="35"/>
+      <c r="H20" s="19">
         <v>20000</v>
       </c>
     </row>
@@ -2400,21 +2431,21 @@
       <c r="B21" s="4">
         <v>46268</v>
       </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="29" t="str">
+      <c r="C21" s="41"/>
+      <c r="D21" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E21" s="29" t="str">
+      <c r="E21" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F21" s="34" t="str">
+      <c r="F21" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G21" s="40"/>
-      <c r="H21" s="21">
+      <c r="G21" s="36"/>
+      <c r="H21" s="20">
         <v>20000</v>
       </c>
     </row>
@@ -2422,21 +2453,21 @@
       <c r="B22" s="2">
         <v>46269</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="27" t="str">
+      <c r="C22" s="40"/>
+      <c r="D22" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E22" s="27" t="str">
+      <c r="E22" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F22" s="28" t="str">
+      <c r="F22" s="27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G22" s="36"/>
-      <c r="H22" s="20">
+      <c r="G22" s="35"/>
+      <c r="H22" s="19">
         <v>20000</v>
       </c>
     </row>
@@ -2444,21 +2475,21 @@
       <c r="B23" s="2">
         <v>46270</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="27" t="str">
+      <c r="C23" s="40"/>
+      <c r="D23" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E23" s="27" t="str">
+      <c r="E23" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F23" s="28" t="str">
+      <c r="F23" s="27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G23" s="36"/>
-      <c r="H23" s="20">
+      <c r="G23" s="35"/>
+      <c r="H23" s="19">
         <v>20000</v>
       </c>
     </row>
@@ -2466,21 +2497,21 @@
       <c r="B24" s="4">
         <v>46271</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="29" t="str">
+      <c r="C24" s="41"/>
+      <c r="D24" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E24" s="29" t="str">
+      <c r="E24" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F24" s="34" t="str">
+      <c r="F24" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G24" s="40"/>
-      <c r="H24" s="21">
+      <c r="G24" s="36"/>
+      <c r="H24" s="20">
         <v>20000</v>
       </c>
     </row>
@@ -2488,21 +2519,21 @@
       <c r="B25" s="2">
         <v>46272</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="27" t="str">
+      <c r="C25" s="40"/>
+      <c r="D25" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E25" s="27" t="str">
+      <c r="E25" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F25" s="28" t="str">
+      <c r="F25" s="27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G25" s="36"/>
-      <c r="H25" s="20">
+      <c r="G25" s="35"/>
+      <c r="H25" s="19">
         <v>20000</v>
       </c>
     </row>
@@ -2510,21 +2541,21 @@
       <c r="B26" s="5">
         <v>46273</v>
       </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="30" t="str">
+      <c r="C26" s="42"/>
+      <c r="D26" s="29" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E26" s="30" t="str">
+      <c r="E26" s="29" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F26" s="31" t="str">
+      <c r="F26" s="30" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="22">
+      <c r="G26" s="37"/>
+      <c r="H26" s="21">
         <v>20000</v>
       </c>
     </row>
@@ -2532,25 +2563,26 @@
       <c r="B27" s="6">
         <v>46274</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8" t="str">
+      <c r="C27" s="38"/>
+      <c r="D27" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E27" s="8" t="str">
+      <c r="E27" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F27" s="19" t="str">
+      <c r="F27" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="41">
+      <c r="G27" s="38"/>
+      <c r="H27" s="34">
         <v>20000</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <conditionalFormatting sqref="D4:D27">
     <cfRule type="colorScale" priority="3">
       <colorScale>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719647DD-2FB2-4A66-B5F7-EB2947207B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDAC44D-483B-4CFB-BF8D-B3683335F09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>Count</t>
   </si>
@@ -100,6 +100,30 @@
   </si>
   <si>
     <t>Daily Target</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Introduction</t>
+  </si>
+  <si>
+    <t>Lit. Review</t>
+  </si>
+  <si>
+    <t>Methodology</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>Discussion</t>
+  </si>
+  <si>
+    <t>Conclusion</t>
+  </si>
+  <si>
+    <t>Section Counts</t>
   </si>
 </sst>
 </file>
@@ -199,7 +223,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -387,11 +411,132 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -455,6 +600,22 @@
     <xf numFmtId="3" fontId="1" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,8 +624,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFE1DECD"/>
       <color rgb="FFF49E9E"/>
-      <color rgb="FFE1DECD"/>
       <color rgb="FFFFFF99"/>
       <color rgb="FF63BE7B"/>
       <color rgb="FFFFEB84"/>
@@ -711,7 +872,7 @@
                   <c:v>5610</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5786</c:v>
+                  <c:v>5988</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1576,7 +1737,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>219808</xdr:colOff>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -1923,7 +2084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA3A3B3-C19C-41F0-9C7A-3F939AAD4664}">
-  <dimension ref="B1:K27"/>
+  <dimension ref="B1:P27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="24" customWidth="1"/>
@@ -1937,10 +2098,15 @@
     <col min="9" max="9" width="2.85546875" style="24" customWidth="1"/>
     <col min="10" max="10" width="27.140625" style="24" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.85546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="24"/>
+    <col min="12" max="12" width="3.5703125" style="24" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" style="24"/>
+    <col min="15" max="15" width="11.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.42578125" style="24" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
       <c r="D1" s="24"/>
@@ -1948,7 +2114,7 @@
       <c r="F1" s="24"/>
       <c r="G1" s="24"/>
     </row>
-    <row r="2" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="32" t="s">
         <v>1</v>
       </c>
@@ -1977,8 +2143,14 @@
         <f>COUNTIF(C3:C27, "")</f>
         <v>18</v>
       </c>
+      <c r="M2" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="52"/>
     </row>
-    <row r="3" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
         <v>46250</v>
       </c>
@@ -2007,8 +2179,20 @@
         <f>COUNTIF(C3:C19, "")</f>
         <v>10</v>
       </c>
+      <c r="M3" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="43">
+        <v>0</v>
+      </c>
+      <c r="O3" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" s="43">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>46251</v>
       </c>
@@ -2038,10 +2222,22 @@
       </c>
       <c r="K4" s="12" cm="1">
         <f t="array" ref="K4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
-        <v>14214</v>
+        <v>14012</v>
+      </c>
+      <c r="M4" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="44">
+        <v>0</v>
+      </c>
+      <c r="O4" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="P4" s="44">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>46252</v>
       </c>
@@ -2071,10 +2267,22 @@
       </c>
       <c r="K5" s="9">
         <f>ROUNDUP(K4/K3,0)</f>
-        <v>1422</v>
+        <v>1402</v>
+      </c>
+      <c r="M5" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="44">
+        <v>5610</v>
+      </c>
+      <c r="O5" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="45">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>46253</v>
       </c>
@@ -2104,10 +2312,18 @@
       </c>
       <c r="K6" s="8">
         <f>ROUNDUP(K4/K2,0)</f>
-        <v>790</v>
-      </c>
+        <v>779</v>
+      </c>
+      <c r="M6" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="45">
+        <v>378</v>
+      </c>
+      <c r="O6" s="46"/>
+      <c r="P6" s="46"/>
     </row>
-    <row r="7" spans="2:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>46254</v>
       </c>
@@ -2133,7 +2349,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>46255</v>
       </c>
@@ -2159,24 +2375,25 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>46256</v>
       </c>
       <c r="C9" s="40">
-        <v>5786</v>
+        <f>SUM(P3:P5,N3:N6)</f>
+        <v>5988</v>
       </c>
       <c r="D9" s="26">
         <f t="shared" si="1"/>
-        <v>176</v>
+        <v>378</v>
       </c>
       <c r="E9" s="26">
         <f t="shared" si="2"/>
-        <v>1214</v>
+        <v>1012</v>
       </c>
       <c r="F9" s="27">
         <f t="shared" ref="F9:F27" si="3">IF(G9="","",IF(C9="","",D9/(G9-C8)))</f>
-        <v>0.12661870503597122</v>
+        <v>0.27194244604316548</v>
       </c>
       <c r="G9" s="35">
         <v>7000</v>
@@ -2185,7 +2402,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>46257</v>
       </c>
@@ -2207,7 +2424,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B11" s="2">
         <v>46258</v>
       </c>
@@ -2229,7 +2446,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B12" s="2">
         <v>46259</v>
       </c>
@@ -2251,7 +2468,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>46260</v>
       </c>
@@ -2273,7 +2490,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="14" spans="2:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>46261</v>
       </c>
@@ -2295,7 +2512,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B15" s="2">
         <v>46262</v>
       </c>
@@ -2317,7 +2534,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B16" s="2">
         <v>46263</v>
       </c>
@@ -2582,7 +2799,9 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="M2:P2"/>
+  </mergeCells>
   <conditionalFormatting sqref="D4:D27">
     <cfRule type="colorScale" priority="3">
       <colorScale>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDAC44D-483B-4CFB-BF8D-B3683335F09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D92CD62-3146-4DED-964B-43D5E3E48440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -536,7 +536,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -556,9 +556,9 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -575,7 +575,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -603,7 +603,6 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -872,7 +871,7 @@
                   <c:v>5610</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5988</c:v>
+                  <c:v>6407</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2143,12 +2142,12 @@
         <f>COUNTIF(C3:C27, "")</f>
         <v>18</v>
       </c>
-      <c r="M2" s="50" t="s">
+      <c r="M2" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="52"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="51"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -2179,13 +2178,13 @@
         <f>COUNTIF(C3:C19, "")</f>
         <v>10</v>
       </c>
-      <c r="M3" s="47" t="s">
+      <c r="M3" s="46" t="s">
         <v>13</v>
       </c>
       <c r="N3" s="43">
         <v>0</v>
       </c>
-      <c r="O3" s="47" t="s">
+      <c r="O3" s="46" t="s">
         <v>17</v>
       </c>
       <c r="P3" s="43">
@@ -2222,15 +2221,15 @@
       </c>
       <c r="K4" s="12" cm="1">
         <f t="array" ref="K4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
-        <v>14012</v>
-      </c>
-      <c r="M4" s="48" t="s">
+        <v>13593</v>
+      </c>
+      <c r="M4" s="47" t="s">
         <v>14</v>
       </c>
       <c r="N4" s="44">
         <v>0</v>
       </c>
-      <c r="O4" s="48" t="s">
+      <c r="O4" s="47" t="s">
         <v>18</v>
       </c>
       <c r="P4" s="44">
@@ -2267,15 +2266,15 @@
       </c>
       <c r="K5" s="9">
         <f>ROUNDUP(K4/K3,0)</f>
-        <v>1402</v>
-      </c>
-      <c r="M5" s="48" t="s">
+        <v>1360</v>
+      </c>
+      <c r="M5" s="47" t="s">
         <v>15</v>
       </c>
       <c r="N5" s="44">
         <v>5610</v>
       </c>
-      <c r="O5" s="49" t="s">
+      <c r="O5" s="48" t="s">
         <v>19</v>
       </c>
       <c r="P5" s="45">
@@ -2312,16 +2311,14 @@
       </c>
       <c r="K6" s="8">
         <f>ROUNDUP(K4/K2,0)</f>
-        <v>779</v>
-      </c>
-      <c r="M6" s="49" t="s">
+        <v>756</v>
+      </c>
+      <c r="M6" s="48" t="s">
         <v>16</v>
       </c>
       <c r="N6" s="45">
-        <v>378</v>
-      </c>
-      <c r="O6" s="46"/>
-      <c r="P6" s="46"/>
+        <v>797</v>
+      </c>
     </row>
     <row r="7" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
@@ -2381,19 +2378,19 @@
       </c>
       <c r="C9" s="40">
         <f>SUM(P3:P5,N3:N6)</f>
-        <v>5988</v>
+        <v>6407</v>
       </c>
       <c r="D9" s="26">
         <f t="shared" si="1"/>
-        <v>378</v>
+        <v>797</v>
       </c>
       <c r="E9" s="26">
         <f t="shared" si="2"/>
-        <v>1012</v>
+        <v>593</v>
       </c>
       <c r="F9" s="27">
         <f t="shared" ref="F9:F27" si="3">IF(G9="","",IF(C9="","",D9/(G9-C8)))</f>
-        <v>0.27194244604316548</v>
+        <v>0.57338129496402879</v>
       </c>
       <c r="G9" s="35">
         <v>7000</v>
@@ -2826,6 +2823,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F4:F27">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.75"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K5">
     <cfRule type="colorScale" priority="5">
       <colorScale>
@@ -2850,18 +2859,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F27">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.75"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D92CD62-3146-4DED-964B-43D5E3E48440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0851E42B-1DC2-4256-90AE-A56ED6D7E731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -871,6 +872,9 @@
                   <c:v>5610</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>6407</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>6407</c:v>
                 </c:pt>
               </c:numCache>
@@ -2140,7 +2144,7 @@
       </c>
       <c r="K2" s="10">
         <f>COUNTIF(C3:C27, "")</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M2" s="49" t="s">
         <v>20</v>
@@ -2176,7 +2180,7 @@
       </c>
       <c r="K3" s="11">
         <f>COUNTIF(C3:C19, "")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M3" s="46" t="s">
         <v>13</v>
@@ -2266,7 +2270,7 @@
       </c>
       <c r="K5" s="9">
         <f>ROUNDUP(K4/K3,0)</f>
-        <v>1360</v>
+        <v>1511</v>
       </c>
       <c r="M5" s="47" t="s">
         <v>15</v>
@@ -2311,7 +2315,7 @@
       </c>
       <c r="K6" s="8">
         <f>ROUNDUP(K4/K2,0)</f>
-        <v>756</v>
+        <v>800</v>
       </c>
       <c r="M6" s="48" t="s">
         <v>16</v>
@@ -2377,7 +2381,6 @@
         <v>46256</v>
       </c>
       <c r="C9" s="40">
-        <f>SUM(P3:P5,N3:N6)</f>
         <v>6407</v>
       </c>
       <c r="D9" s="26">
@@ -2403,20 +2406,25 @@
       <c r="B10" s="4">
         <v>46257</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="28" t="str">
+      <c r="C10" s="40">
+        <f>SUM($P$3:$P$5,$N$3:$N$6)</f>
+        <v>6407</v>
+      </c>
+      <c r="D10" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E10" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="E10" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F10" s="33" t="str">
+        <v>1593</v>
+      </c>
+      <c r="F10" s="33">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G10" s="36"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="36">
+        <v>8000</v>
+      </c>
       <c r="H10" s="20">
         <v>20000</v>
       </c>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0851E42B-1DC2-4256-90AE-A56ED6D7E731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A9FBF2-2F3F-492A-8DEB-740DBCAF41B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -62,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>Count</t>
   </si>
@@ -125,6 +124,9 @@
   </si>
   <si>
     <t>Section Counts</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -224,7 +226,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -533,11 +535,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -616,6 +674,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -875,7 +944,7 @@
                   <c:v>6407</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6407</c:v>
+                  <c:v>6792</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2225,7 +2294,7 @@
       </c>
       <c r="K4" s="12" cm="1">
         <f t="array" ref="K4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
-        <v>13593</v>
+        <v>13208</v>
       </c>
       <c r="M4" s="47" t="s">
         <v>14</v>
@@ -2270,7 +2339,7 @@
       </c>
       <c r="K5" s="9">
         <f>ROUNDUP(K4/K3,0)</f>
-        <v>1511</v>
+        <v>1468</v>
       </c>
       <c r="M5" s="47" t="s">
         <v>15</v>
@@ -2278,10 +2347,10 @@
       <c r="N5" s="44">
         <v>5610</v>
       </c>
-      <c r="O5" s="48" t="s">
+      <c r="O5" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="58">
         <v>0</v>
       </c>
     </row>
@@ -2315,13 +2384,20 @@
       </c>
       <c r="K6" s="8">
         <f>ROUNDUP(K4/K2,0)</f>
-        <v>800</v>
+        <v>777</v>
       </c>
       <c r="M6" s="48" t="s">
         <v>16</v>
       </c>
       <c r="N6" s="45">
-        <v>797</v>
+        <v>1182</v>
+      </c>
+      <c r="O6" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="60">
+        <f>SUM($P$3:$P$5,$N$3:$N$6)</f>
+        <v>6792</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="15" x14ac:dyDescent="0.25">
@@ -2406,21 +2482,21 @@
       <c r="B10" s="4">
         <v>46257</v>
       </c>
-      <c r="C10" s="40">
-        <f>SUM($P$3:$P$5,$N$3:$N$6)</f>
-        <v>6407</v>
+      <c r="C10" s="41">
+        <f>P6</f>
+        <v>6792</v>
       </c>
       <c r="D10" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="E10" s="28">
         <f t="shared" si="2"/>
-        <v>1593</v>
+        <v>1208</v>
       </c>
       <c r="F10" s="33">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.24168236032642812</v>
       </c>
       <c r="G10" s="36">
         <v>8000</v>
@@ -2451,25 +2527,25 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B12" s="2">
+    <row r="12" spans="2:16" ht="15" x14ac:dyDescent="0.25">
+      <c r="B12" s="4">
         <v>46259</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="26" t="str">
+      <c r="C12" s="41"/>
+      <c r="D12" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E12" s="26" t="str">
+      <c r="E12" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F12" s="27" t="str">
+      <c r="F12" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G12" s="35"/>
-      <c r="H12" s="19">
+      <c r="G12" s="36"/>
+      <c r="H12" s="20">
         <v>20000</v>
       </c>
     </row>
@@ -2605,25 +2681,25 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="6">
+    <row r="19" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="52">
         <v>46266</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="7" t="str">
+      <c r="C19" s="53"/>
+      <c r="D19" s="54" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E19" s="7" t="str">
+      <c r="E19" s="54" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F19" s="18" t="str">
+      <c r="F19" s="55" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="34">
+      <c r="G19" s="53"/>
+      <c r="H19" s="56">
         <v>20000</v>
       </c>
     </row>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A9FBF2-2F3F-492A-8DEB-740DBCAF41B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434353D0-1863-4AF8-8F18-97168102192C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -944,7 +944,7 @@
                   <c:v>6407</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6792</c:v>
+                  <c:v>6710</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="K4" s="12" cm="1">
         <f t="array" ref="K4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
-        <v>13208</v>
+        <v>13290</v>
       </c>
       <c r="M4" s="47" t="s">
         <v>14</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="K5" s="9">
         <f>ROUNDUP(K4/K3,0)</f>
-        <v>1468</v>
+        <v>1477</v>
       </c>
       <c r="M5" s="47" t="s">
         <v>15</v>
@@ -2384,20 +2384,20 @@
       </c>
       <c r="K6" s="8">
         <f>ROUNDUP(K4/K2,0)</f>
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="M6" s="48" t="s">
         <v>16</v>
       </c>
       <c r="N6" s="45">
-        <v>1182</v>
+        <v>1100</v>
       </c>
       <c r="O6" s="59" t="s">
         <v>21</v>
       </c>
       <c r="P6" s="60">
         <f>SUM($P$3:$P$5,$N$3:$N$6)</f>
-        <v>6792</v>
+        <v>6710</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="15" x14ac:dyDescent="0.25">
@@ -2484,19 +2484,19 @@
       </c>
       <c r="C10" s="41">
         <f>P6</f>
-        <v>6792</v>
+        <v>6710</v>
       </c>
       <c r="D10" s="28">
         <f t="shared" si="1"/>
-        <v>385</v>
+        <v>303</v>
       </c>
       <c r="E10" s="28">
         <f t="shared" si="2"/>
-        <v>1208</v>
+        <v>1290</v>
       </c>
       <c r="F10" s="33">
         <f t="shared" si="3"/>
-        <v>0.24168236032642812</v>
+        <v>0.19020715630885121</v>
       </c>
       <c r="G10" s="36">
         <v>8000</v>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434353D0-1863-4AF8-8F18-97168102192C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE1D312-CF33-45DE-B9C7-7C397F06515C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -665,15 +665,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
@@ -685,6 +676,15 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -944,7 +944,10 @@
                   <c:v>6407</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6710</c:v>
+                  <c:v>7066</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7230</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2213,14 +2216,14 @@
       </c>
       <c r="K2" s="10">
         <f>COUNTIF(C3:C27, "")</f>
-        <v>17</v>
-      </c>
-      <c r="M2" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="51"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="60"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -2249,7 +2252,7 @@
       </c>
       <c r="K3" s="11">
         <f>COUNTIF(C3:C19, "")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M3" s="46" t="s">
         <v>13</v>
@@ -2294,7 +2297,7 @@
       </c>
       <c r="K4" s="12" cm="1">
         <f t="array" ref="K4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
-        <v>13290</v>
+        <v>12770</v>
       </c>
       <c r="M4" s="47" t="s">
         <v>14</v>
@@ -2339,7 +2342,7 @@
       </c>
       <c r="K5" s="9">
         <f>ROUNDUP(K4/K3,0)</f>
-        <v>1477</v>
+        <v>1597</v>
       </c>
       <c r="M5" s="47" t="s">
         <v>15</v>
@@ -2347,10 +2350,10 @@
       <c r="N5" s="44">
         <v>5610</v>
       </c>
-      <c r="O5" s="57" t="s">
+      <c r="O5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="58">
+      <c r="P5" s="55">
         <v>0</v>
       </c>
     </row>
@@ -2384,20 +2387,20 @@
       </c>
       <c r="K6" s="8">
         <f>ROUNDUP(K4/K2,0)</f>
-        <v>782</v>
+        <v>799</v>
       </c>
       <c r="M6" s="48" t="s">
         <v>16</v>
       </c>
       <c r="N6" s="45">
-        <v>1100</v>
-      </c>
-      <c r="O6" s="59" t="s">
+        <v>1620</v>
+      </c>
+      <c r="O6" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="57">
         <f>SUM($P$3:$P$5,$N$3:$N$6)</f>
-        <v>6710</v>
+        <v>7230</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="15" x14ac:dyDescent="0.25">
@@ -2483,20 +2486,19 @@
         <v>46257</v>
       </c>
       <c r="C10" s="41">
-        <f>P6</f>
-        <v>6710</v>
+        <v>7066</v>
       </c>
       <c r="D10" s="28">
         <f t="shared" si="1"/>
-        <v>303</v>
+        <v>659</v>
       </c>
       <c r="E10" s="28">
         <f t="shared" si="2"/>
-        <v>1290</v>
+        <v>934</v>
       </c>
       <c r="F10" s="33">
         <f t="shared" si="3"/>
-        <v>0.19020715630885121</v>
+        <v>0.41368487131198994</v>
       </c>
       <c r="G10" s="36">
         <v>8000</v>
@@ -2505,24 +2507,29 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>46258</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="26" t="str">
+      <c r="C11" s="41">
+        <f>$P$6</f>
+        <v>7230</v>
+      </c>
+      <c r="D11" s="26">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E11" s="26" t="str">
+        <v>164</v>
+      </c>
+      <c r="E11" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F11" s="27" t="str">
+        <v>1270</v>
+      </c>
+      <c r="F11" s="27">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G11" s="35"/>
+        <v>0.11436541143654114</v>
+      </c>
+      <c r="G11" s="35">
+        <v>8500</v>
+      </c>
       <c r="H11" s="19">
         <v>20000</v>
       </c>
@@ -2682,24 +2689,24 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="52">
+      <c r="B19" s="49">
         <v>46266</v>
       </c>
-      <c r="C19" s="53"/>
-      <c r="D19" s="54" t="str">
+      <c r="C19" s="50"/>
+      <c r="D19" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E19" s="54" t="str">
+      <c r="E19" s="51" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F19" s="55" t="str">
+      <c r="F19" s="52" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G19" s="53"/>
-      <c r="H19" s="56">
+      <c r="G19" s="50"/>
+      <c r="H19" s="53">
         <v>20000</v>
       </c>
     </row>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE1D312-CF33-45DE-B9C7-7C397F06515C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66491DE-42E9-4CC2-B0F3-3B9BEF1318EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -947,7 +947,10 @@
                   <c:v>7066</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7230</c:v>
+                  <c:v>7218</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7753</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2216,7 +2219,7 @@
       </c>
       <c r="K2" s="10">
         <f>COUNTIF(C3:C27, "")</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M2" s="58" t="s">
         <v>20</v>
@@ -2252,7 +2255,7 @@
       </c>
       <c r="K3" s="11">
         <f>COUNTIF(C3:C19, "")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M3" s="46" t="s">
         <v>13</v>
@@ -2297,7 +2300,7 @@
       </c>
       <c r="K4" s="12" cm="1">
         <f t="array" ref="K4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
-        <v>12770</v>
+        <v>12247</v>
       </c>
       <c r="M4" s="47" t="s">
         <v>14</v>
@@ -2342,13 +2345,13 @@
       </c>
       <c r="K5" s="9">
         <f>ROUNDUP(K4/K3,0)</f>
-        <v>1597</v>
+        <v>1750</v>
       </c>
       <c r="M5" s="47" t="s">
         <v>15</v>
       </c>
       <c r="N5" s="44">
-        <v>5610</v>
+        <v>5612</v>
       </c>
       <c r="O5" s="54" t="s">
         <v>19</v>
@@ -2387,20 +2390,20 @@
       </c>
       <c r="K6" s="8">
         <f>ROUNDUP(K4/K2,0)</f>
-        <v>799</v>
+        <v>817</v>
       </c>
       <c r="M6" s="48" t="s">
         <v>16</v>
       </c>
       <c r="N6" s="45">
-        <v>1620</v>
+        <v>2141</v>
       </c>
       <c r="O6" s="56" t="s">
         <v>21</v>
       </c>
       <c r="P6" s="57">
         <f>SUM($P$3:$P$5,$N$3:$N$6)</f>
-        <v>7230</v>
+        <v>7753</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="15" x14ac:dyDescent="0.25">
@@ -2512,20 +2515,19 @@
         <v>46258</v>
       </c>
       <c r="C11" s="41">
-        <f>$P$6</f>
-        <v>7230</v>
+        <v>7218</v>
       </c>
       <c r="D11" s="26">
         <f t="shared" si="1"/>
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E11" s="26">
         <f t="shared" si="2"/>
-        <v>1270</v>
+        <v>1282</v>
       </c>
       <c r="F11" s="27">
         <f t="shared" si="3"/>
-        <v>0.11436541143654114</v>
+        <v>0.10599721059972106</v>
       </c>
       <c r="G11" s="35">
         <v>8500</v>
@@ -2538,20 +2540,25 @@
       <c r="B12" s="4">
         <v>46259</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="28" t="str">
+      <c r="C12" s="41">
+        <f>P6</f>
+        <v>7753</v>
+      </c>
+      <c r="D12" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E12" s="28" t="str">
+        <v>535</v>
+      </c>
+      <c r="E12" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F12" s="33" t="str">
+        <v>747</v>
+      </c>
+      <c r="F12" s="33">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G12" s="36"/>
+        <v>0.41731669266770671</v>
+      </c>
+      <c r="G12" s="36">
+        <v>8500</v>
+      </c>
       <c r="H12" s="20">
         <v>20000</v>
       </c>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66491DE-42E9-4CC2-B0F3-3B9BEF1318EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA35CD16-F248-4098-A12C-C3ABF73C2BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -36,28 +36,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -950,7 +928,10 @@
                   <c:v>7218</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7753</c:v>
+                  <c:v>8459</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8459</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2219,7 +2200,7 @@
       </c>
       <c r="K2" s="10">
         <f>COUNTIF(C3:C27, "")</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M2" s="58" t="s">
         <v>20</v>
@@ -2255,7 +2236,7 @@
       </c>
       <c r="K3" s="11">
         <f>COUNTIF(C3:C19, "")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M3" s="46" t="s">
         <v>13</v>
@@ -2298,9 +2279,9 @@
       <c r="J4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="12" cm="1">
-        <f t="array" ref="K4">MAX(0,20000-LOOKUP(2,1/(C3:C27&lt;&gt;""),C3:C27))</f>
-        <v>12247</v>
+      <c r="K4" s="12">
+        <f>MAX(0,20000-P6)</f>
+        <v>11541</v>
       </c>
       <c r="M4" s="47" t="s">
         <v>14</v>
@@ -2345,13 +2326,13 @@
       </c>
       <c r="K5" s="9">
         <f>ROUNDUP(K4/K3,0)</f>
-        <v>1750</v>
+        <v>1924</v>
       </c>
       <c r="M5" s="47" t="s">
         <v>15</v>
       </c>
       <c r="N5" s="44">
-        <v>5612</v>
+        <v>5614</v>
       </c>
       <c r="O5" s="54" t="s">
         <v>19</v>
@@ -2390,20 +2371,20 @@
       </c>
       <c r="K6" s="8">
         <f>ROUNDUP(K4/K2,0)</f>
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="M6" s="48" t="s">
         <v>16</v>
       </c>
       <c r="N6" s="45">
-        <v>2141</v>
+        <v>2845</v>
       </c>
       <c r="O6" s="56" t="s">
         <v>21</v>
       </c>
       <c r="P6" s="57">
         <f>SUM($P$3:$P$5,$N$3:$N$6)</f>
-        <v>7753</v>
+        <v>8459</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="15" x14ac:dyDescent="0.25">
@@ -2541,20 +2522,19 @@
         <v>46259</v>
       </c>
       <c r="C12" s="41">
-        <f>P6</f>
-        <v>7753</v>
+        <v>8459</v>
       </c>
       <c r="D12" s="28">
         <f t="shared" si="1"/>
-        <v>535</v>
+        <v>1241</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" si="2"/>
-        <v>747</v>
+        <v>41</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="3"/>
-        <v>0.41731669266770671</v>
+        <v>0.96801872074883</v>
       </c>
       <c r="G12" s="36">
         <v>8500</v>
@@ -2567,20 +2547,25 @@
       <c r="B13" s="2">
         <v>46260</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="26" t="str">
+      <c r="C13" s="40">
+        <f>P6</f>
+        <v>8459</v>
+      </c>
+      <c r="D13" s="26">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E13" s="26" t="str">
+        <v>0</v>
+      </c>
+      <c r="E13" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F13" s="27" t="str">
+        <v>1541</v>
+      </c>
+      <c r="F13" s="27">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G13" s="35"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="35">
+        <v>10000</v>
+      </c>
       <c r="H13" s="19">
         <v>20000</v>
       </c>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA35CD16-F248-4098-A12C-C3ABF73C2BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7180AE4A-15A2-4C69-928C-D034CF6F94B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>Count</t>
   </si>
@@ -106,6 +106,9 @@
   <si>
     <t>Total</t>
   </si>
+  <si>
+    <t>Total Daily Target</t>
+  </si>
 </sst>
 </file>
 
@@ -114,7 +117,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,6 +133,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -573,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -663,6 +673,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -671,8 +690,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFF49E9E"/>
       <color rgb="FFE1DECD"/>
-      <color rgb="FFF49E9E"/>
       <color rgb="FFFFFF99"/>
       <color rgb="FF63BE7B"/>
       <color rgb="FFFFEB84"/>
@@ -931,7 +950,10 @@
                   <c:v>8459</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8459</c:v>
+                  <c:v>8780</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9647</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -948,7 +970,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$H$2</c:f>
+              <c:f>Sheet1!$I$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -971,7 +993,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$3:$H$27</c:f>
+              <c:f>Sheet1!$I$3:$I$27</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="25"/>
@@ -1789,13 +1811,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>183173</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>187933</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2143,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA3A3B3-C19C-41F0-9C7A-3F939AAD4664}">
-  <dimension ref="B1:P27"/>
+  <dimension ref="B1:Q27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="24" customWidth="1"/>
@@ -2152,28 +2174,30 @@
     <col min="4" max="4" width="15.7109375" style="23" customWidth="1"/>
     <col min="5" max="5" width="27" style="23" customWidth="1"/>
     <col min="6" max="6" width="15.140625" style="23" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="23" customWidth="1"/>
-    <col min="8" max="8" width="16" style="24" customWidth="1"/>
-    <col min="9" max="9" width="2.85546875" style="24" customWidth="1"/>
-    <col min="10" max="10" width="27.140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.5703125" style="24" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" style="24"/>
-    <col min="15" max="15" width="11.42578125" style="24" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.42578125" style="24" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="24"/>
+    <col min="7" max="7" width="19.140625" style="23" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" style="23" customWidth="1"/>
+    <col min="9" max="9" width="16" style="24" customWidth="1"/>
+    <col min="10" max="10" width="2.85546875" style="24" customWidth="1"/>
+    <col min="11" max="11" width="27.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.5703125" style="24" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="24"/>
+    <col min="16" max="16" width="11.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.42578125" style="24" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
       <c r="D1" s="24"/>
       <c r="E1" s="24"/>
       <c r="F1" s="24"/>
       <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
-    <row r="2" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="32" t="s">
         <v>1</v>
       </c>
@@ -2190,26 +2214,29 @@
         <v>11</v>
       </c>
       <c r="G2" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="I2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="K2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="10">
+      <c r="L2" s="10">
         <f>COUNTIF(C3:C27, "")</f>
-        <v>14</v>
-      </c>
-      <c r="M2" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="59"/>
       <c r="O2" s="59"/>
-      <c r="P2" s="60"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="60"/>
     </row>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
         <v>46250</v>
       </c>
@@ -2225,33 +2252,34 @@
       <c r="F3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="61"/>
+      <c r="H3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="20">
+      <c r="I3" s="20">
         <v>20000</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="K3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="11">
+      <c r="L3" s="11">
         <f>COUNTIF(C3:C19, "")</f>
-        <v>6</v>
-      </c>
-      <c r="M3" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="N3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="43">
+      <c r="O3" s="43">
         <v>0</v>
       </c>
-      <c r="O3" s="46" t="s">
+      <c r="P3" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="43">
+      <c r="Q3" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>46251</v>
       </c>
@@ -2263,40 +2291,44 @@
         <v>841</v>
       </c>
       <c r="E4" s="26">
-        <f>IF(C4="", "", G4-C4)</f>
+        <f>IF(C4="", "", H4-C4)</f>
         <v>-165</v>
       </c>
       <c r="F4" s="27">
-        <f t="shared" ref="F4:F8" si="0">IF(G4="","",IF(C4="","",D4/(G4-C3)))</f>
+        <f>IF(H4="","",IF(C4="","",D4/(H4-C3)))</f>
         <v>1.2440828402366864</v>
       </c>
-      <c r="G4" s="35">
+      <c r="G4" s="63">
+        <f t="shared" ref="G4:G13" si="0">H4-C3</f>
+        <v>676</v>
+      </c>
+      <c r="H4" s="35">
         <v>2200</v>
       </c>
-      <c r="H4" s="19">
+      <c r="I4" s="19">
         <v>20000</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="K4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="12">
-        <f>MAX(0,20000-P6)</f>
-        <v>11541</v>
-      </c>
-      <c r="M4" s="47" t="s">
+      <c r="L4" s="12">
+        <f>MAX(0,20000-Q6)</f>
+        <v>10353</v>
+      </c>
+      <c r="N4" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="44">
+      <c r="O4" s="44">
         <v>0</v>
       </c>
-      <c r="O4" s="47" t="s">
+      <c r="P4" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="44">
+      <c r="Q4" s="44">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>46252</v>
       </c>
@@ -2308,40 +2340,44 @@
         <v>633</v>
       </c>
       <c r="E5" s="26">
-        <f t="shared" ref="E5:E27" si="2">IF(C5="", "", G5-C5)</f>
+        <f>IF(C5="", "", H5-C5)</f>
         <v>202</v>
       </c>
       <c r="F5" s="27">
+        <f>IF(H5="","",IF(C5="","",D5/(H5-C4)))</f>
+        <v>0.75808383233532939</v>
+      </c>
+      <c r="G5" s="63">
         <f t="shared" si="0"/>
-        <v>0.75808383233532939</v>
-      </c>
-      <c r="G5" s="35">
+        <v>835</v>
+      </c>
+      <c r="H5" s="35">
         <v>3200</v>
       </c>
-      <c r="H5" s="19">
+      <c r="I5" s="19">
         <v>20000</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="K5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="9">
-        <f>ROUNDUP(K4/K3,0)</f>
-        <v>1924</v>
-      </c>
-      <c r="M5" s="47" t="s">
+      <c r="L5" s="9">
+        <f>ROUNDUP(L4/L3,0)</f>
+        <v>2071</v>
+      </c>
+      <c r="N5" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="44">
-        <v>5614</v>
-      </c>
-      <c r="O5" s="54" t="s">
+      <c r="O5" s="44">
+        <v>5622</v>
+      </c>
+      <c r="P5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="55">
+      <c r="Q5" s="55">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>46253</v>
       </c>
@@ -2353,41 +2389,45 @@
         <v>613</v>
       </c>
       <c r="E6" s="26">
-        <f t="shared" si="2"/>
+        <f>IF(C6="", "", H6-C6)</f>
         <v>389</v>
       </c>
       <c r="F6" s="27">
+        <f>IF(H6="","",IF(C6="","",D6/(H6-C5)))</f>
+        <v>0.61177644710578838</v>
+      </c>
+      <c r="G6" s="63">
         <f t="shared" si="0"/>
-        <v>0.61177644710578838</v>
-      </c>
-      <c r="G6" s="35">
+        <v>1002</v>
+      </c>
+      <c r="H6" s="35">
         <v>4000</v>
       </c>
-      <c r="H6" s="19">
+      <c r="I6" s="19">
         <v>20000</v>
       </c>
-      <c r="J6" s="17" t="s">
+      <c r="K6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="8">
-        <f>ROUNDUP(K4/K2,0)</f>
-        <v>825</v>
-      </c>
-      <c r="M6" s="48" t="s">
+      <c r="L6" s="8">
+        <f>ROUNDUP(L4/L2,0)</f>
+        <v>797</v>
+      </c>
+      <c r="N6" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="45">
-        <v>2845</v>
-      </c>
-      <c r="O6" s="56" t="s">
+      <c r="O6" s="45">
+        <v>4025</v>
+      </c>
+      <c r="P6" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="P6" s="57">
-        <f>SUM($P$3:$P$5,$N$3:$N$6)</f>
-        <v>8459</v>
+      <c r="Q6" s="57">
+        <f>SUM($Q$3:$Q$5,$O$3:$O$6)</f>
+        <v>9647</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" ht="15" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>46254</v>
       </c>
@@ -2399,21 +2439,25 @@
         <v>1439</v>
       </c>
       <c r="E7" s="28">
-        <f t="shared" si="2"/>
+        <f>IF(C7="", "", H7-C7)</f>
         <v>-50</v>
       </c>
       <c r="F7" s="33">
+        <f>IF(H7="","",IF(C7="","",D7/(H7-C6)))</f>
+        <v>1.0359971202303815</v>
+      </c>
+      <c r="G7" s="66">
         <f t="shared" si="0"/>
-        <v>1.0359971202303815</v>
-      </c>
-      <c r="G7" s="36">
+        <v>1389</v>
+      </c>
+      <c r="H7" s="36">
         <v>5000</v>
       </c>
-      <c r="H7" s="20">
+      <c r="I7" s="20">
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>46255</v>
       </c>
@@ -2425,21 +2469,25 @@
         <v>560</v>
       </c>
       <c r="E8" s="26">
-        <f t="shared" si="2"/>
+        <f>IF(C8="", "", H8-C8)</f>
         <v>790</v>
       </c>
       <c r="F8" s="27">
+        <f>IF(H8="","",IF(C8="","",D8/(H8-C7)))</f>
+        <v>0.4148148148148148</v>
+      </c>
+      <c r="G8" s="63">
         <f t="shared" si="0"/>
-        <v>0.4148148148148148</v>
-      </c>
-      <c r="G8" s="35">
+        <v>1350</v>
+      </c>
+      <c r="H8" s="35">
         <v>6400</v>
       </c>
-      <c r="H8" s="19">
+      <c r="I8" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>46256</v>
       </c>
@@ -2451,21 +2499,25 @@
         <v>797</v>
       </c>
       <c r="E9" s="26">
-        <f t="shared" si="2"/>
+        <f>IF(C9="", "", H9-C9)</f>
         <v>593</v>
       </c>
       <c r="F9" s="27">
-        <f t="shared" ref="F9:F27" si="3">IF(G9="","",IF(C9="","",D9/(G9-C8)))</f>
+        <f>IF(H9="","",IF(C9="","",D9/(H9-C8)))</f>
         <v>0.57338129496402879</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="63">
+        <f t="shared" si="0"/>
+        <v>1390</v>
+      </c>
+      <c r="H9" s="35">
         <v>7000</v>
       </c>
-      <c r="H9" s="19">
+      <c r="I9" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="10" spans="2:16" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" ht="15" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>46257</v>
       </c>
@@ -2477,25 +2529,29 @@
         <v>659</v>
       </c>
       <c r="E10" s="28">
-        <f t="shared" si="2"/>
+        <f>IF(C10="", "", H10-C10)</f>
         <v>934</v>
       </c>
       <c r="F10" s="33">
-        <f t="shared" si="3"/>
+        <f>IF(H10="","",IF(C10="","",D10/(H10-C9)))</f>
         <v>0.41368487131198994</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="66">
+        <f t="shared" si="0"/>
+        <v>1593</v>
+      </c>
+      <c r="H10" s="36">
         <v>8000</v>
       </c>
-      <c r="H10" s="20">
+      <c r="I10" s="20">
         <v>20000</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B11" s="2">
         <v>46258</v>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="67">
         <v>7218</v>
       </c>
       <c r="D11" s="26">
@@ -2503,21 +2559,25 @@
         <v>152</v>
       </c>
       <c r="E11" s="26">
-        <f t="shared" si="2"/>
+        <f>IF(C11="", "", H11-C11)</f>
         <v>1282</v>
       </c>
       <c r="F11" s="27">
-        <f t="shared" si="3"/>
+        <f>IF(H11="","",IF(C11="","",D11/(H11-C10)))</f>
         <v>0.10599721059972106</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="63">
+        <f t="shared" si="0"/>
+        <v>1434</v>
+      </c>
+      <c r="H11" s="35">
         <v>8500</v>
       </c>
-      <c r="H11" s="19">
+      <c r="I11" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" ht="15" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>46259</v>
       </c>
@@ -2529,70 +2589,86 @@
         <v>1241</v>
       </c>
       <c r="E12" s="28">
-        <f t="shared" si="2"/>
+        <f>IF(C12="", "", H12-C12)</f>
         <v>41</v>
       </c>
       <c r="F12" s="33">
-        <f t="shared" si="3"/>
+        <f>IF(H12="","",IF(C12="","",D12/(H12-C11)))</f>
         <v>0.96801872074883</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="66">
+        <f t="shared" si="0"/>
+        <v>1282</v>
+      </c>
+      <c r="H12" s="36">
         <v>8500</v>
       </c>
-      <c r="H12" s="20">
+      <c r="I12" s="20">
         <v>20000</v>
       </c>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>46260</v>
       </c>
       <c r="C13" s="40">
-        <f>P6</f>
-        <v>8459</v>
+        <v>8780</v>
       </c>
       <c r="D13" s="26">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E13" s="26">
-        <f t="shared" si="2"/>
+        <f>IF(C13="", "", H13-C13)</f>
+        <v>1220</v>
+      </c>
+      <c r="F13" s="27">
+        <f>IF(H13="","",IF(C13="","",D13/(H13-C12)))</f>
+        <v>0.20830629461388708</v>
+      </c>
+      <c r="G13" s="63">
+        <f t="shared" si="0"/>
         <v>1541</v>
       </c>
-      <c r="F13" s="27">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="35">
+      <c r="H13" s="35">
         <v>10000</v>
       </c>
-      <c r="H13" s="19">
+      <c r="I13" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" ht="15" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>46261</v>
       </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="28" t="str">
+      <c r="C14" s="40">
+        <f>Q$6</f>
+        <v>9647</v>
+      </c>
+      <c r="D14" s="28">
         <f>IF(C14="", "", C14-C13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="28" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F14" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G14" s="36"/>
-      <c r="H14" s="20">
+        <v>867</v>
+      </c>
+      <c r="E14" s="28">
+        <f>IF(C14="", "", H14-C14)</f>
+        <v>1353</v>
+      </c>
+      <c r="F14" s="33">
+        <f>IF(H14="","",IF(C14="","",D14/(H14-C13)))</f>
+        <v>0.39054054054054055</v>
+      </c>
+      <c r="G14" s="66">
+        <f>H14-C13</f>
+        <v>2220</v>
+      </c>
+      <c r="H14" s="36">
+        <v>11000</v>
+      </c>
+      <c r="I14" s="20">
         <v>20000</v>
       </c>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B15" s="2">
         <v>46262</v>
       </c>
@@ -2602,19 +2678,20 @@
         <v/>
       </c>
       <c r="E15" s="26" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C15="", "", H15-C15)</f>
         <v/>
       </c>
       <c r="F15" s="27" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G15" s="35"/>
-      <c r="H15" s="19">
+        <f>IF(H15="","",IF(C15="","",D15/(H15-C14)))</f>
+        <v/>
+      </c>
+      <c r="G15" s="63"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B16" s="2">
         <v>46263</v>
       </c>
@@ -2624,19 +2701,20 @@
         <v/>
       </c>
       <c r="E16" s="26" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C16="", "", H16-C16)</f>
         <v/>
       </c>
       <c r="F16" s="27" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G16" s="35"/>
-      <c r="H16" s="19">
+        <f>IF(H16="","",IF(C16="","",D16/(H16-C15)))</f>
+        <v/>
+      </c>
+      <c r="G16" s="63"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>46264</v>
       </c>
@@ -2646,19 +2724,20 @@
         <v/>
       </c>
       <c r="E17" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C17="", "", H17-C17)</f>
         <v/>
       </c>
       <c r="F17" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G17" s="36"/>
-      <c r="H17" s="20">
+        <f>IF(H17="","",IF(C17="","",D17/(H17-C16)))</f>
+        <v/>
+      </c>
+      <c r="G17" s="66"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="20">
         <v>20000</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="5">
         <v>46265</v>
       </c>
@@ -2668,19 +2747,20 @@
         <v/>
       </c>
       <c r="E18" s="29" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C18="", "", H18-C18)</f>
         <v/>
       </c>
       <c r="F18" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G18" s="37"/>
-      <c r="H18" s="21">
+        <f>IF(H18="","",IF(C18="","",D18/(H18-C17)))</f>
+        <v/>
+      </c>
+      <c r="G18" s="64"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="21">
         <v>20000</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="49">
         <v>46266</v>
       </c>
@@ -2690,19 +2770,20 @@
         <v/>
       </c>
       <c r="E19" s="51" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C19="", "", H19-C19)</f>
         <v/>
       </c>
       <c r="F19" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G19" s="50"/>
-      <c r="H19" s="53">
+        <f>IF(H19="","",IF(C19="","",D19/(H19-C18)))</f>
+        <v/>
+      </c>
+      <c r="G19" s="65"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="53">
         <v>20000</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="1">
         <v>46267</v>
       </c>
@@ -2712,19 +2793,20 @@
         <v/>
       </c>
       <c r="E20" s="26" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C20="", "", H20-C20)</f>
         <v/>
       </c>
       <c r="F20" s="27" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G20" s="35"/>
-      <c r="H20" s="19">
+        <f>IF(H20="","",IF(C20="","",D20/(H20-C19)))</f>
+        <v/>
+      </c>
+      <c r="G20" s="63"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>46268</v>
       </c>
@@ -2734,19 +2816,20 @@
         <v/>
       </c>
       <c r="E21" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C21="", "", H21-C21)</f>
         <v/>
       </c>
       <c r="F21" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G21" s="36"/>
-      <c r="H21" s="20">
+        <f>IF(H21="","",IF(C21="","",D21/(H21-C20)))</f>
+        <v/>
+      </c>
+      <c r="G21" s="66"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="20">
         <v>20000</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="2">
         <v>46269</v>
       </c>
@@ -2756,19 +2839,20 @@
         <v/>
       </c>
       <c r="E22" s="26" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C22="", "", H22-C22)</f>
         <v/>
       </c>
       <c r="F22" s="27" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G22" s="35"/>
-      <c r="H22" s="19">
+        <f>IF(H22="","",IF(C22="","",D22/(H22-C21)))</f>
+        <v/>
+      </c>
+      <c r="G22" s="63"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B23" s="2">
         <v>46270</v>
       </c>
@@ -2778,19 +2862,20 @@
         <v/>
       </c>
       <c r="E23" s="26" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C23="", "", H23-C23)</f>
         <v/>
       </c>
       <c r="F23" s="27" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G23" s="35"/>
-      <c r="H23" s="19">
+        <f>IF(H23="","",IF(C23="","",D23/(H23-C22)))</f>
+        <v/>
+      </c>
+      <c r="G23" s="63"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>46271</v>
       </c>
@@ -2800,19 +2885,20 @@
         <v/>
       </c>
       <c r="E24" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C24="", "", H24-C24)</f>
         <v/>
       </c>
       <c r="F24" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G24" s="36"/>
-      <c r="H24" s="20">
+        <f>IF(H24="","",IF(C24="","",D24/(H24-C23)))</f>
+        <v/>
+      </c>
+      <c r="G24" s="66"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="20">
         <v>20000</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B25" s="2">
         <v>46272</v>
       </c>
@@ -2822,19 +2908,20 @@
         <v/>
       </c>
       <c r="E25" s="26" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C25="", "", H25-C25)</f>
         <v/>
       </c>
       <c r="F25" s="27" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G25" s="35"/>
-      <c r="H25" s="19">
+        <f>IF(H25="","",IF(C25="","",D25/(H25-C24)))</f>
+        <v/>
+      </c>
+      <c r="G25" s="63"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="5">
         <v>46273</v>
       </c>
@@ -2844,19 +2931,20 @@
         <v/>
       </c>
       <c r="E26" s="29" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C26="", "", H26-C26)</f>
         <v/>
       </c>
       <c r="F26" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G26" s="37"/>
-      <c r="H26" s="21">
+        <f>IF(H26="","",IF(C26="","",D26/(H26-C25)))</f>
+        <v/>
+      </c>
+      <c r="G26" s="64"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="21">
         <v>20000</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B27" s="6">
         <v>46274</v>
       </c>
@@ -2866,21 +2954,22 @@
         <v/>
       </c>
       <c r="E27" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C27="", "", H27-C27)</f>
         <v/>
       </c>
       <c r="F27" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G27" s="38"/>
-      <c r="H27" s="34">
+        <f>IF(H27="","",IF(C27="","",D27/(H27-C26)))</f>
+        <v/>
+      </c>
+      <c r="G27" s="62"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="34">
         <v>20000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="N2:Q2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D27">
     <cfRule type="colorScale" priority="3">
@@ -2918,7 +3007,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5">
+  <conditionalFormatting sqref="L5">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="100"/>
@@ -2930,7 +3019,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6">
+  <conditionalFormatting sqref="L6">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2943,6 +3032,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7180AE4A-15A2-4C69-928C-D034CF6F94B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A573B77-8F23-4118-9FA3-4252068B2F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="300" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
@@ -664,6 +664,15 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -672,15 +681,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -954,6 +954,18 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>9647</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9647</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9647</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9647</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>11228</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2227,14 +2239,14 @@
       </c>
       <c r="L2" s="10">
         <f>COUNTIF(C3:C27, "")</f>
-        <v>13</v>
-      </c>
-      <c r="N2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="60"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="67"/>
     </row>
     <row r="3" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -2252,7 +2264,7 @@
       <c r="F3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="61"/>
+      <c r="G3" s="58"/>
       <c r="H3" s="25" t="s">
         <v>8</v>
       </c>
@@ -2264,7 +2276,7 @@
       </c>
       <c r="L3" s="11">
         <f>COUNTIF(C3:C19, "")</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N3" s="46" t="s">
         <v>13</v>
@@ -2291,15 +2303,15 @@
         <v>841</v>
       </c>
       <c r="E4" s="26">
-        <f>IF(C4="", "", H4-C4)</f>
+        <f t="shared" ref="E4:E27" si="0">IF(C4="", "", H4-C4)</f>
         <v>-165</v>
       </c>
       <c r="F4" s="27">
-        <f>IF(H4="","",IF(C4="","",D4/(H4-C3)))</f>
+        <f t="shared" ref="F4:F27" si="1">IF(H4="","",IF(C4="","",D4/(H4-C3)))</f>
         <v>1.2440828402366864</v>
       </c>
-      <c r="G4" s="63">
-        <f t="shared" ref="G4:G13" si="0">H4-C3</f>
+      <c r="G4" s="60">
+        <f t="shared" ref="G4:G13" si="2">H4-C3</f>
         <v>676</v>
       </c>
       <c r="H4" s="35">
@@ -2313,7 +2325,7 @@
       </c>
       <c r="L4" s="12">
         <f>MAX(0,20000-Q6)</f>
-        <v>10353</v>
+        <v>8772</v>
       </c>
       <c r="N4" s="47" t="s">
         <v>14</v>
@@ -2336,19 +2348,19 @@
         <v>2998</v>
       </c>
       <c r="D5" s="26">
-        <f t="shared" ref="D5:D27" si="1">IF(C5="", "", C5-C4)</f>
+        <f t="shared" ref="D5:D27" si="3">IF(C5="", "", C5-C4)</f>
         <v>633</v>
       </c>
       <c r="E5" s="26">
-        <f>IF(C5="", "", H5-C5)</f>
+        <f t="shared" si="0"/>
         <v>202</v>
       </c>
       <c r="F5" s="27">
-        <f>IF(H5="","",IF(C5="","",D5/(H5-C4)))</f>
+        <f t="shared" si="1"/>
         <v>0.75808383233532939</v>
       </c>
-      <c r="G5" s="63">
-        <f t="shared" si="0"/>
+      <c r="G5" s="60">
+        <f t="shared" si="2"/>
         <v>835</v>
       </c>
       <c r="H5" s="35">
@@ -2362,7 +2374,7 @@
       </c>
       <c r="L5" s="9">
         <f>ROUNDUP(L4/L3,0)</f>
-        <v>2071</v>
+        <v>8772</v>
       </c>
       <c r="N5" s="47" t="s">
         <v>15</v>
@@ -2385,19 +2397,19 @@
         <v>3611</v>
       </c>
       <c r="D6" s="26">
+        <f t="shared" si="3"/>
+        <v>613</v>
+      </c>
+      <c r="E6" s="26">
+        <f t="shared" si="0"/>
+        <v>389</v>
+      </c>
+      <c r="F6" s="27">
         <f t="shared" si="1"/>
-        <v>613</v>
-      </c>
-      <c r="E6" s="26">
-        <f>IF(C6="", "", H6-C6)</f>
-        <v>389</v>
-      </c>
-      <c r="F6" s="27">
-        <f>IF(H6="","",IF(C6="","",D6/(H6-C5)))</f>
         <v>0.61177644710578838</v>
       </c>
-      <c r="G6" s="63">
-        <f t="shared" si="0"/>
+      <c r="G6" s="60">
+        <f t="shared" si="2"/>
         <v>1002</v>
       </c>
       <c r="H6" s="35">
@@ -2411,20 +2423,20 @@
       </c>
       <c r="L6" s="8">
         <f>ROUNDUP(L4/L2,0)</f>
-        <v>797</v>
+        <v>975</v>
       </c>
       <c r="N6" s="48" t="s">
         <v>16</v>
       </c>
       <c r="O6" s="45">
-        <v>4025</v>
+        <v>5606</v>
       </c>
       <c r="P6" s="56" t="s">
         <v>21</v>
       </c>
       <c r="Q6" s="57">
         <f>SUM($Q$3:$Q$5,$O$3:$O$6)</f>
-        <v>9647</v>
+        <v>11228</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="15" x14ac:dyDescent="0.25">
@@ -2435,19 +2447,19 @@
         <v>5050</v>
       </c>
       <c r="D7" s="28">
+        <f t="shared" si="3"/>
+        <v>1439</v>
+      </c>
+      <c r="E7" s="28">
+        <f t="shared" si="0"/>
+        <v>-50</v>
+      </c>
+      <c r="F7" s="33">
         <f t="shared" si="1"/>
-        <v>1439</v>
-      </c>
-      <c r="E7" s="28">
-        <f>IF(C7="", "", H7-C7)</f>
-        <v>-50</v>
-      </c>
-      <c r="F7" s="33">
-        <f>IF(H7="","",IF(C7="","",D7/(H7-C6)))</f>
         <v>1.0359971202303815</v>
       </c>
-      <c r="G7" s="66">
-        <f t="shared" si="0"/>
+      <c r="G7" s="63">
+        <f t="shared" si="2"/>
         <v>1389</v>
       </c>
       <c r="H7" s="36">
@@ -2465,19 +2477,19 @@
         <v>5610</v>
       </c>
       <c r="D8" s="26">
+        <f t="shared" si="3"/>
+        <v>560</v>
+      </c>
+      <c r="E8" s="26">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="F8" s="27">
         <f t="shared" si="1"/>
-        <v>560</v>
-      </c>
-      <c r="E8" s="26">
-        <f>IF(C8="", "", H8-C8)</f>
-        <v>790</v>
-      </c>
-      <c r="F8" s="27">
-        <f>IF(H8="","",IF(C8="","",D8/(H8-C7)))</f>
         <v>0.4148148148148148</v>
       </c>
-      <c r="G8" s="63">
-        <f t="shared" si="0"/>
+      <c r="G8" s="60">
+        <f t="shared" si="2"/>
         <v>1350</v>
       </c>
       <c r="H8" s="35">
@@ -2495,19 +2507,19 @@
         <v>6407</v>
       </c>
       <c r="D9" s="26">
+        <f t="shared" si="3"/>
+        <v>797</v>
+      </c>
+      <c r="E9" s="26">
+        <f t="shared" si="0"/>
+        <v>593</v>
+      </c>
+      <c r="F9" s="27">
         <f t="shared" si="1"/>
-        <v>797</v>
-      </c>
-      <c r="E9" s="26">
-        <f>IF(C9="", "", H9-C9)</f>
-        <v>593</v>
-      </c>
-      <c r="F9" s="27">
-        <f>IF(H9="","",IF(C9="","",D9/(H9-C8)))</f>
         <v>0.57338129496402879</v>
       </c>
-      <c r="G9" s="63">
-        <f t="shared" si="0"/>
+      <c r="G9" s="60">
+        <f t="shared" si="2"/>
         <v>1390</v>
       </c>
       <c r="H9" s="35">
@@ -2525,19 +2537,19 @@
         <v>7066</v>
       </c>
       <c r="D10" s="28">
+        <f t="shared" si="3"/>
+        <v>659</v>
+      </c>
+      <c r="E10" s="28">
+        <f t="shared" si="0"/>
+        <v>934</v>
+      </c>
+      <c r="F10" s="33">
         <f t="shared" si="1"/>
-        <v>659</v>
-      </c>
-      <c r="E10" s="28">
-        <f>IF(C10="", "", H10-C10)</f>
-        <v>934</v>
-      </c>
-      <c r="F10" s="33">
-        <f>IF(H10="","",IF(C10="","",D10/(H10-C9)))</f>
         <v>0.41368487131198994</v>
       </c>
-      <c r="G10" s="66">
-        <f t="shared" si="0"/>
+      <c r="G10" s="63">
+        <f t="shared" si="2"/>
         <v>1593</v>
       </c>
       <c r="H10" s="36">
@@ -2551,23 +2563,23 @@
       <c r="B11" s="2">
         <v>46258</v>
       </c>
-      <c r="C11" s="67">
+      <c r="C11" s="64">
         <v>7218</v>
       </c>
       <c r="D11" s="26">
+        <f t="shared" si="3"/>
+        <v>152</v>
+      </c>
+      <c r="E11" s="26">
+        <f t="shared" si="0"/>
+        <v>1282</v>
+      </c>
+      <c r="F11" s="27">
         <f t="shared" si="1"/>
-        <v>152</v>
-      </c>
-      <c r="E11" s="26">
-        <f>IF(C11="", "", H11-C11)</f>
-        <v>1282</v>
-      </c>
-      <c r="F11" s="27">
-        <f>IF(H11="","",IF(C11="","",D11/(H11-C10)))</f>
         <v>0.10599721059972106</v>
       </c>
-      <c r="G11" s="63">
-        <f t="shared" si="0"/>
+      <c r="G11" s="60">
+        <f t="shared" si="2"/>
         <v>1434</v>
       </c>
       <c r="H11" s="35">
@@ -2585,19 +2597,19 @@
         <v>8459</v>
       </c>
       <c r="D12" s="28">
+        <f t="shared" si="3"/>
+        <v>1241</v>
+      </c>
+      <c r="E12" s="28">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>1241</v>
-      </c>
-      <c r="E12" s="28">
-        <f>IF(C12="", "", H12-C12)</f>
-        <v>41</v>
-      </c>
-      <c r="F12" s="33">
-        <f>IF(H12="","",IF(C12="","",D12/(H12-C11)))</f>
         <v>0.96801872074883</v>
       </c>
-      <c r="G12" s="66">
-        <f t="shared" si="0"/>
+      <c r="G12" s="63">
+        <f t="shared" si="2"/>
         <v>1282</v>
       </c>
       <c r="H12" s="36">
@@ -2615,19 +2627,19 @@
         <v>8780</v>
       </c>
       <c r="D13" s="26">
+        <f t="shared" si="3"/>
+        <v>321</v>
+      </c>
+      <c r="E13" s="26">
+        <f t="shared" si="0"/>
+        <v>1220</v>
+      </c>
+      <c r="F13" s="27">
         <f t="shared" si="1"/>
-        <v>321</v>
-      </c>
-      <c r="E13" s="26">
-        <f>IF(C13="", "", H13-C13)</f>
-        <v>1220</v>
-      </c>
-      <c r="F13" s="27">
-        <f>IF(H13="","",IF(C13="","",D13/(H13-C12)))</f>
         <v>0.20830629461388708</v>
       </c>
-      <c r="G13" s="63">
-        <f t="shared" si="0"/>
+      <c r="G13" s="60">
+        <f t="shared" si="2"/>
         <v>1541</v>
       </c>
       <c r="H13" s="35">
@@ -2642,7 +2654,6 @@
         <v>46261</v>
       </c>
       <c r="C14" s="40">
-        <f>Q$6</f>
         <v>9647</v>
       </c>
       <c r="D14" s="28">
@@ -2650,14 +2661,14 @@
         <v>867</v>
       </c>
       <c r="E14" s="28">
-        <f>IF(C14="", "", H14-C14)</f>
+        <f t="shared" si="0"/>
         <v>1353</v>
       </c>
       <c r="F14" s="33">
-        <f>IF(H14="","",IF(C14="","",D14/(H14-C13)))</f>
+        <f t="shared" si="1"/>
         <v>0.39054054054054055</v>
       </c>
-      <c r="G14" s="66">
+      <c r="G14" s="63">
         <f>H14-C13</f>
         <v>2220</v>
       </c>
@@ -2672,20 +2683,22 @@
       <c r="B15" s="2">
         <v>46262</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="26" t="str">
+      <c r="C15" s="40">
+        <v>9647</v>
+      </c>
+      <c r="D15" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="26">
+        <f t="shared" si="0"/>
+        <v>-9647</v>
+      </c>
+      <c r="F15" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E15" s="26" t="str">
-        <f>IF(C15="", "", H15-C15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="27" t="str">
-        <f>IF(H15="","",IF(C15="","",D15/(H15-C14)))</f>
-        <v/>
-      </c>
-      <c r="G15" s="63"/>
+      <c r="G15" s="60"/>
       <c r="H15" s="35"/>
       <c r="I15" s="19">
         <v>20000</v>
@@ -2695,20 +2708,22 @@
       <c r="B16" s="2">
         <v>46263</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="26" t="str">
+      <c r="C16" s="40">
+        <v>9647</v>
+      </c>
+      <c r="D16" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="26">
+        <f t="shared" si="0"/>
+        <v>-9647</v>
+      </c>
+      <c r="F16" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E16" s="26" t="str">
-        <f>IF(C16="", "", H16-C16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="27" t="str">
-        <f>IF(H16="","",IF(C16="","",D16/(H16-C15)))</f>
-        <v/>
-      </c>
-      <c r="G16" s="63"/>
+      <c r="G16" s="60"/>
       <c r="H16" s="35"/>
       <c r="I16" s="19">
         <v>20000</v>
@@ -2718,20 +2733,22 @@
       <c r="B17" s="4">
         <v>46264</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="28" t="str">
+      <c r="C17" s="40">
+        <v>9647</v>
+      </c>
+      <c r="D17" s="28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="28">
+        <f t="shared" si="0"/>
+        <v>-9647</v>
+      </c>
+      <c r="F17" s="33" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E17" s="28" t="str">
-        <f>IF(C17="", "", H17-C17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="33" t="str">
-        <f>IF(H17="","",IF(C17="","",D17/(H17-C16)))</f>
-        <v/>
-      </c>
-      <c r="G17" s="66"/>
+      <c r="G17" s="63"/>
       <c r="H17" s="36"/>
       <c r="I17" s="20">
         <v>20000</v>
@@ -2741,21 +2758,26 @@
       <c r="B18" s="5">
         <v>46265</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="29" t="str">
+      <c r="C18" s="42">
+        <f>Q6</f>
+        <v>11228</v>
+      </c>
+      <c r="D18" s="29">
+        <f t="shared" si="3"/>
+        <v>1581</v>
+      </c>
+      <c r="E18" s="29">
+        <f t="shared" si="0"/>
+        <v>772</v>
+      </c>
+      <c r="F18" s="30">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E18" s="29" t="str">
-        <f>IF(C18="", "", H18-C18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="30" t="str">
-        <f>IF(H18="","",IF(C18="","",D18/(H18-C17)))</f>
-        <v/>
-      </c>
-      <c r="G18" s="64"/>
-      <c r="H18" s="37"/>
+        <v>0.67190820229494264</v>
+      </c>
+      <c r="G18" s="61"/>
+      <c r="H18" s="37">
+        <v>12000</v>
+      </c>
       <c r="I18" s="21">
         <v>20000</v>
       </c>
@@ -2766,18 +2788,18 @@
       </c>
       <c r="C19" s="50"/>
       <c r="D19" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="E19" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F19" s="52" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E19" s="51" t="str">
-        <f>IF(C19="", "", H19-C19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="52" t="str">
-        <f>IF(H19="","",IF(C19="","",D19/(H19-C18)))</f>
-        <v/>
-      </c>
-      <c r="G19" s="65"/>
+      <c r="G19" s="62"/>
       <c r="H19" s="50"/>
       <c r="I19" s="53">
         <v>20000</v>
@@ -2789,18 +2811,18 @@
       </c>
       <c r="C20" s="35"/>
       <c r="D20" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="E20" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F20" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E20" s="26" t="str">
-        <f>IF(C20="", "", H20-C20)</f>
-        <v/>
-      </c>
-      <c r="F20" s="27" t="str">
-        <f>IF(H20="","",IF(C20="","",D20/(H20-C19)))</f>
-        <v/>
-      </c>
-      <c r="G20" s="63"/>
+      <c r="G20" s="60"/>
       <c r="H20" s="35"/>
       <c r="I20" s="19">
         <v>20000</v>
@@ -2812,18 +2834,18 @@
       </c>
       <c r="C21" s="41"/>
       <c r="D21" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="E21" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F21" s="33" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E21" s="28" t="str">
-        <f>IF(C21="", "", H21-C21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="33" t="str">
-        <f>IF(H21="","",IF(C21="","",D21/(H21-C20)))</f>
-        <v/>
-      </c>
-      <c r="G21" s="66"/>
+      <c r="G21" s="63"/>
       <c r="H21" s="36"/>
       <c r="I21" s="20">
         <v>20000</v>
@@ -2835,18 +2857,18 @@
       </c>
       <c r="C22" s="40"/>
       <c r="D22" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="E22" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F22" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E22" s="26" t="str">
-        <f>IF(C22="", "", H22-C22)</f>
-        <v/>
-      </c>
-      <c r="F22" s="27" t="str">
-        <f>IF(H22="","",IF(C22="","",D22/(H22-C21)))</f>
-        <v/>
-      </c>
-      <c r="G22" s="63"/>
+      <c r="G22" s="60"/>
       <c r="H22" s="35"/>
       <c r="I22" s="19">
         <v>20000</v>
@@ -2858,18 +2880,18 @@
       </c>
       <c r="C23" s="40"/>
       <c r="D23" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="E23" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F23" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E23" s="26" t="str">
-        <f>IF(C23="", "", H23-C23)</f>
-        <v/>
-      </c>
-      <c r="F23" s="27" t="str">
-        <f>IF(H23="","",IF(C23="","",D23/(H23-C22)))</f>
-        <v/>
-      </c>
-      <c r="G23" s="63"/>
+      <c r="G23" s="60"/>
       <c r="H23" s="35"/>
       <c r="I23" s="19">
         <v>20000</v>
@@ -2881,18 +2903,18 @@
       </c>
       <c r="C24" s="41"/>
       <c r="D24" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="E24" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F24" s="33" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E24" s="28" t="str">
-        <f>IF(C24="", "", H24-C24)</f>
-        <v/>
-      </c>
-      <c r="F24" s="33" t="str">
-        <f>IF(H24="","",IF(C24="","",D24/(H24-C23)))</f>
-        <v/>
-      </c>
-      <c r="G24" s="66"/>
+      <c r="G24" s="63"/>
       <c r="H24" s="36"/>
       <c r="I24" s="20">
         <v>20000</v>
@@ -2904,18 +2926,18 @@
       </c>
       <c r="C25" s="40"/>
       <c r="D25" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="E25" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F25" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E25" s="26" t="str">
-        <f>IF(C25="", "", H25-C25)</f>
-        <v/>
-      </c>
-      <c r="F25" s="27" t="str">
-        <f>IF(H25="","",IF(C25="","",D25/(H25-C24)))</f>
-        <v/>
-      </c>
-      <c r="G25" s="63"/>
+      <c r="G25" s="60"/>
       <c r="H25" s="35"/>
       <c r="I25" s="19">
         <v>20000</v>
@@ -2927,18 +2949,18 @@
       </c>
       <c r="C26" s="42"/>
       <c r="D26" s="29" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="E26" s="29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F26" s="30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E26" s="29" t="str">
-        <f>IF(C26="", "", H26-C26)</f>
-        <v/>
-      </c>
-      <c r="F26" s="30" t="str">
-        <f>IF(H26="","",IF(C26="","",D26/(H26-C25)))</f>
-        <v/>
-      </c>
-      <c r="G26" s="64"/>
+      <c r="G26" s="61"/>
       <c r="H26" s="37"/>
       <c r="I26" s="21">
         <v>20000</v>
@@ -2950,18 +2972,18 @@
       </c>
       <c r="C27" s="38"/>
       <c r="D27" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="E27" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F27" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E27" s="7" t="str">
-        <f>IF(C27="", "", H27-C27)</f>
-        <v/>
-      </c>
-      <c r="F27" s="18" t="str">
-        <f>IF(H27="","",IF(C27="","",D27/(H27-C26)))</f>
-        <v/>
-      </c>
-      <c r="G27" s="62"/>
+      <c r="G27" s="59"/>
       <c r="H27" s="38"/>
       <c r="I27" s="34">
         <v>20000</v>

--- a/thesis/Word Count Tracker.xlsx
+++ b/thesis/Word Count Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\wesle\biomedical_kg_thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A573B77-8F23-4118-9FA3-4252068B2F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488D4DDD-479C-4D99-8C3A-34A7AE58085B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
+    <workbookView xWindow="28680" yWindow="1875" windowWidth="29040" windowHeight="15840" xr2:uid="{9A934C0C-D068-49A2-992C-A9C72EA321F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -583,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -682,6 +682,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -966,6 +967,12 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>11228</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>11644</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>13500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2184,9 +2191,9 @@
     <col min="2" max="2" width="22.85546875" style="22" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" style="23" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" style="23" customWidth="1"/>
-    <col min="5" max="5" width="27" style="23" customWidth="1"/>
+    <col min="5" max="5" width="27" style="23" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="15.140625" style="23" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" style="23" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" style="23" customWidth="1"/>
     <col min="8" max="8" width="15.85546875" style="23" customWidth="1"/>
     <col min="9" max="9" width="16" style="24" customWidth="1"/>
     <col min="10" max="10" width="2.85546875" style="24" customWidth="1"/>
@@ -2239,7 +2246,7 @@
       </c>
       <c r="L2" s="10">
         <f>COUNTIF(C3:C27, "")</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N2" s="65" t="s">
         <v>20</v>
@@ -2276,7 +2283,7 @@
       </c>
       <c r="L3" s="11">
         <f>COUNTIF(C3:C19, "")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="46" t="s">
         <v>13</v>
@@ -2325,7 +2332,7 @@
       </c>
       <c r="L4" s="12">
         <f>MAX(0,20000-Q6)</f>
-        <v>8772</v>
+        <v>8356</v>
       </c>
       <c r="N4" s="47" t="s">
         <v>14</v>
@@ -2372,9 +2379,9 @@
       <c r="K5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="9" t="e">
         <f>ROUNDUP(L4/L3,0)</f>
-        <v>8772</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N5" s="47" t="s">
         <v>15</v>
@@ -2423,20 +2430,20 @@
       </c>
       <c r="L6" s="8">
         <f>ROUNDUP(L4/L2,0)</f>
-        <v>975</v>
+        <v>1194</v>
       </c>
       <c r="N6" s="48" t="s">
         <v>16</v>
       </c>
       <c r="O6" s="45">
-        <v>5606</v>
+        <v>6022</v>
       </c>
       <c r="P6" s="56" t="s">
         <v>21</v>
       </c>
       <c r="Q6" s="57">
         <f>SUM($Q$3:$Q$5,$O$3:$O$6)</f>
-        <v>11228</v>
+        <v>11644</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="15" x14ac:dyDescent="0.25">
@@ -2759,7 +2766,6 @@
         <v>46265</v>
       </c>
       <c r="C18" s="42">
-        <f>Q6</f>
         <v>11228</v>
       </c>
       <c r="D18" s="29">
@@ -2786,14 +2792,17 @@
       <c r="B19" s="49">
         <v>46266</v>
       </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="51" t="str">
+      <c r="C19" s="50">
+        <f>Q6</f>
+        <v>11644</v>
+      </c>
+      <c r="D19" s="51">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="E19" s="51" t="str">
+        <v>416</v>
+      </c>
+      <c r="E19" s="51">
         <f t="shared" si="0"/>
-        <v/>
+        <v>-11644</v>
       </c>
       <c r="F19" s="52" t="str">
         <f t="shared" si="1"/>
@@ -2809,14 +2818,16 @@
       <c r="B20" s="1">
         <v>46267</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="26" t="str">
+      <c r="C20" s="35">
+        <v>13500</v>
+      </c>
+      <c r="D20" s="26">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="E20" s="26" t="str">
+        <v>1856</v>
+      </c>
+      <c r="E20" s="26">
         <f t="shared" si="0"/>
-        <v/>
+        <v>-13500</v>
       </c>
       <c r="F20" s="27" t="str">
         <f t="shared" si="1"/>
@@ -2920,8 +2931,8 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="2">
+    <row r="25" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="B25" s="4">
         <v>46272</v>
       </c>
       <c r="C25" s="40"/>
@@ -2943,8 +2954,8 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="5">
+    <row r="26" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="68">
         <v>46273</v>
       </c>
       <c r="C26" s="42"/>
@@ -2997,8 +3008,8 @@
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="500"/>
-        <cfvo type="num" val="900"/>
-        <cfvo type="num" val="1300"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="num" val="$L$4/$L$2"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
